--- a/generated_reports/monthly_attendance_report_march_2026_construction.xlsx
+++ b/generated_reports/monthly_attendance_report_march_2026_construction.xlsx
@@ -8,22 +8,21 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="محمد عرفان مظفر حسين" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="محمد جمعة" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="وزير خان حبيب الله خان" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="عبدالودود عجب خان" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="برينس كومار بانديت بهارات" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="راما كانت ياداف سانترا ج ياداف" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="نظر جان محمد ظاهر" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ارشد على عزيز اور الرحمن" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="محمد مصطفى يوسف  غانم" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="محمد بلال احمد" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="محمد ادريس عجب كل" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name=" محمد عويس شير اكبر" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ميلكامو مولا بيليو" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="امارى ميسقى وبيتو" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="ابابو موجيس نيجيس" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="باجر انجلال شارهان" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name=" كليم الله شيرال" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="وزير خان حبيب الله خان" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="عبدالودود عجب خان" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="برينس كومار بانديت بهارات" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="راما كانت ياداف سانترا ج ياداف" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="نظر جان محمد ظاهر" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ارشد على عزيز اور الرحمن" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="محمد مصطفى يوسف  غانم" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="محمد بلال احمد" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="محمد ادريس عجب كل" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name=" محمد عويس شير اكبر" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ميلكامو مولا بيليو" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="امارى ميسقى وبيتو" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ابابو موجيس نيجيس" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="باجر انجلال شارهان" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name=" كليم الله شيرال" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2589,7 +2588,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>4500</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2620,7 @@
       </c>
       <c r="B4" s="58" t="inlineStr">
         <is>
-          <t>محمد مصطفى يوسف  غانم</t>
+          <t>محمد بلال احمد</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -2753,7 +2752,7 @@
       </c>
       <c r="H8" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I8" s="34">
@@ -2881,7 +2880,7 @@
       </c>
       <c r="H12" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I12" s="34">
@@ -2947,7 +2946,7 @@
       </c>
       <c r="H14" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I14" s="34">
@@ -2979,7 +2978,7 @@
       </c>
       <c r="H15" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I15" s="28">
@@ -3011,7 +3010,7 @@
       </c>
       <c r="H16" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I16" s="34">
@@ -3043,7 +3042,7 @@
       </c>
       <c r="H17" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I17" s="28">
@@ -3075,7 +3074,7 @@
       </c>
       <c r="H18" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I18" s="34">
@@ -3107,7 +3106,7 @@
       </c>
       <c r="H19" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I19" s="28">
@@ -3139,7 +3138,7 @@
       </c>
       <c r="H20" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I20" s="34">
@@ -3173,7 +3172,7 @@
       </c>
       <c r="H21" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I21" s="28">
@@ -3205,7 +3204,7 @@
       </c>
       <c r="H22" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I22" s="34">
@@ -3237,7 +3236,7 @@
       </c>
       <c r="H23" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I23" s="28">
@@ -3269,7 +3268,7 @@
       </c>
       <c r="H24" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I24" s="34">
@@ -3301,7 +3300,7 @@
       </c>
       <c r="H25" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I25" s="28">
@@ -3335,7 +3334,7 @@
       </c>
       <c r="H26" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I26" s="34">
@@ -3369,7 +3368,7 @@
       </c>
       <c r="H27" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I27" s="28">
@@ -3403,7 +3402,7 @@
       </c>
       <c r="H28" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I28" s="34">
@@ -3422,10 +3421,12 @@
       </c>
       <c r="B29" s="68" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="C29" s="68" t="n"/>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C29" s="68" t="n">
+        <v>8</v>
+      </c>
       <c r="D29" s="68" t="n"/>
       <c r="E29" s="68" t="n"/>
       <c r="F29" s="68" t="n"/>
@@ -3433,8 +3434,10 @@
         <f>IF(B29="SL","SL","")</f>
         <v/>
       </c>
-      <c r="H29" s="69" t="n">
-        <v/>
+      <c r="H29" s="69" t="inlineStr">
+        <is>
+          <t>Saeed Al Zubaidi</t>
+        </is>
       </c>
       <c r="I29" s="28">
         <f>IFERROR(IF(SUM(C29:G29)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C29:G29)), "")</f>
@@ -3442,7 +3445,7 @@
       </c>
       <c r="J29" s="70" t="inlineStr">
         <is>
-          <t>Last day was 22 Mar</t>
+          <t>Holiday</t>
         </is>
       </c>
     </row>
@@ -3452,10 +3455,12 @@
       </c>
       <c r="B30" s="71" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="C30" s="72" t="n"/>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C30" s="72" t="n">
+        <v>8</v>
+      </c>
       <c r="D30" s="71" t="n"/>
       <c r="E30" s="74" t="n"/>
       <c r="F30" s="74" t="n"/>
@@ -3463,8 +3468,10 @@
         <f>IF(B30="SL","SL","")</f>
         <v/>
       </c>
-      <c r="H30" s="75" t="n">
-        <v/>
+      <c r="H30" s="75" t="inlineStr">
+        <is>
+          <t>Saeed Al Zubaidi</t>
+        </is>
       </c>
       <c r="I30" s="34">
         <f>IFERROR(IF(SUM(C30:G30)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C30:G30)), "")</f>
@@ -3474,10 +3481,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1" s="44">
-      <c r="A31" s="61" t="n"/>
-      <c r="B31" s="68" t="n"/>
-      <c r="C31" s="68" t="n"/>
+    <row r="31" ht="32" customHeight="1" s="44">
+      <c r="A31" s="61" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B31" s="68" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C31" s="68" t="n">
+        <v>8</v>
+      </c>
       <c r="D31" s="68" t="n"/>
       <c r="E31" s="68" t="n"/>
       <c r="F31" s="68" t="n"/>
@@ -3485,17 +3500,33 @@
         <f>IF(B31="SL","SL","")</f>
         <v/>
       </c>
-      <c r="H31" s="69" t="n"/>
+      <c r="H31" s="69" t="inlineStr">
+        <is>
+          <t>Salem Al Zaabi</t>
+        </is>
+      </c>
       <c r="I31" s="28">
         <f>IFERROR(IF(SUM(C31:G31)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C31:G31)), "")</f>
         <v/>
       </c>
-      <c r="J31" s="96" t="n"/>
-    </row>
-    <row r="32" ht="30" customHeight="1" s="44">
-      <c r="A32" s="62" t="n"/>
-      <c r="B32" s="71" t="n"/>
-      <c r="C32" s="72" t="n"/>
+      <c r="J31" s="70" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1" s="44">
+      <c r="A32" s="62" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B32" s="71" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C32" s="72" t="n">
+        <v>8</v>
+      </c>
       <c r="D32" s="71" t="n"/>
       <c r="E32" s="74" t="n"/>
       <c r="F32" s="74" t="n"/>
@@ -3503,17 +3534,31 @@
         <f>IF(B32="SL","SL","")</f>
         <v/>
       </c>
-      <c r="H32" s="75" t="n"/>
+      <c r="H32" s="75" t="inlineStr">
+        <is>
+          <t>Salem Al Zaabi</t>
+        </is>
+      </c>
       <c r="I32" s="34">
         <f>IFERROR(IF(SUM(C32:G32)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C32:G32)), "")</f>
         <v/>
       </c>
-      <c r="J32" s="96" t="n"/>
-    </row>
-    <row r="33" ht="30" customHeight="1" s="44">
-      <c r="A33" s="61" t="n"/>
-      <c r="B33" s="68" t="n"/>
-      <c r="C33" s="68" t="n"/>
+      <c r="J32" s="70" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1" s="44">
+      <c r="A33" s="61" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B33" s="68" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C33" s="68" t="n">
+        <v>8</v>
+      </c>
       <c r="D33" s="68" t="n"/>
       <c r="E33" s="68" t="n"/>
       <c r="F33" s="68" t="n"/>
@@ -3521,17 +3566,31 @@
         <f>IF(B33="SL","SL","")</f>
         <v/>
       </c>
-      <c r="H33" s="69" t="n"/>
+      <c r="H33" s="69" t="inlineStr">
+        <is>
+          <t>Salem Al Zaabi</t>
+        </is>
+      </c>
       <c r="I33" s="28">
         <f>IFERROR(IF(SUM(C33:G33)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C33:G33)), "")</f>
         <v/>
       </c>
-      <c r="J33" s="96" t="n"/>
-    </row>
-    <row r="34" ht="30" customHeight="1" s="44">
-      <c r="A34" s="62" t="n"/>
-      <c r="B34" s="79" t="n"/>
-      <c r="C34" s="72" t="n"/>
+      <c r="J33" s="70" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1" s="44">
+      <c r="A34" s="62" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B34" s="78" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C34" s="72" t="n">
+        <v>8</v>
+      </c>
       <c r="D34" s="74" t="n"/>
       <c r="E34" s="74" t="n"/>
       <c r="F34" s="74" t="n"/>
@@ -3539,17 +3598,33 @@
         <f>IF(B34="SL","SL","")</f>
         <v/>
       </c>
-      <c r="H34" s="75" t="n"/>
+      <c r="H34" s="75" t="inlineStr">
+        <is>
+          <t>Salem Al Zaabi</t>
+        </is>
+      </c>
       <c r="I34" s="34">
         <f>IFERROR(IF(SUM(C34:G34)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C34:G34)), "")</f>
         <v/>
       </c>
-      <c r="J34" s="96" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1" s="44">
-      <c r="A35" s="61" t="n"/>
-      <c r="B35" s="68" t="n"/>
-      <c r="C35" s="68" t="n"/>
+      <c r="J34" s="70" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1" s="44">
+      <c r="A35" s="61" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B35" s="68" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C35" s="68" t="n">
+        <v>8</v>
+      </c>
       <c r="D35" s="68" t="n"/>
       <c r="E35" s="68" t="n"/>
       <c r="F35" s="68" t="n"/>
@@ -3557,42 +3632,76 @@
         <f>IF(B35="SL","SL","")</f>
         <v/>
       </c>
-      <c r="H35" s="69" t="n"/>
+      <c r="H35" s="69" t="inlineStr">
+        <is>
+          <t>Abdullah Aljunaibi</t>
+        </is>
+      </c>
       <c r="I35" s="28">
         <f>IFERROR(IF(SUM(C35:G35)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C35:G35)), "")</f>
         <v/>
       </c>
-      <c r="J35" s="96" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1" s="44">
-      <c r="A36" s="62" t="n"/>
-      <c r="B36" s="79" t="n"/>
-      <c r="C36" s="72" t="n"/>
+      <c r="J35" s="70" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1" s="44">
+      <c r="A36" s="62" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B36" s="79" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C36" s="72" t="n">
+        <v>8</v>
+      </c>
       <c r="D36" s="74" t="n"/>
       <c r="E36" s="74" t="n"/>
       <c r="F36" s="74" t="n"/>
       <c r="G36" s="29" t="n"/>
-      <c r="H36" s="75" t="n"/>
+      <c r="H36" s="75" t="inlineStr">
+        <is>
+          <t>Salem Al Zaabi</t>
+        </is>
+      </c>
       <c r="I36" s="34">
         <f>IFERROR(IF(SUM(C36:G36)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C36:G36)), "")</f>
         <v/>
       </c>
-      <c r="J36" s="96" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1" s="44">
-      <c r="A37" s="61" t="n"/>
-      <c r="B37" s="68" t="n"/>
-      <c r="C37" s="68" t="n"/>
+      <c r="J36" s="70" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1" s="44">
+      <c r="A37" s="61" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B37" s="68" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C37" s="68" t="n">
+        <v>8</v>
+      </c>
       <c r="D37" s="68" t="n"/>
       <c r="E37" s="68" t="n"/>
       <c r="F37" s="68" t="n"/>
       <c r="G37" s="26" t="n"/>
-      <c r="H37" s="69" t="n"/>
+      <c r="H37" s="69" t="inlineStr">
+        <is>
+          <t>Abdullah Aljunaibi</t>
+        </is>
+      </c>
       <c r="I37" s="28">
         <f>IFERROR(IF(SUM(C37:G37)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C37:G37)), "")</f>
         <v/>
       </c>
-      <c r="J37" s="96" t="n"/>
+      <c r="J37" s="70" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38" ht="30" customHeight="1" s="44">
       <c r="A38" s="54" t="inlineStr">
@@ -3929,7 +4038,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>1200</t>
         </is>
       </c>
     </row>
@@ -3961,7 +4070,7 @@
       </c>
       <c r="B4" s="58" t="inlineStr">
         <is>
-          <t>محمد بلال احمد</t>
+          <t>محمد ادريس عجب كل</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -4061,7 +4170,7 @@
       <c r="G7" s="26" t="n"/>
       <c r="H7" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I7" s="28">
@@ -4093,7 +4202,7 @@
       </c>
       <c r="H8" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I8" s="34">
@@ -4125,7 +4234,7 @@
       </c>
       <c r="H9" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I9" s="28">
@@ -4157,7 +4266,7 @@
       </c>
       <c r="H10" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I10" s="34">
@@ -4180,7 +4289,9 @@
       <c r="C11" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="68" t="n"/>
+      <c r="D11" s="68" t="n">
+        <v>3</v>
+      </c>
       <c r="E11" s="68" t="n"/>
       <c r="F11" s="68" t="n"/>
       <c r="G11" s="26">
@@ -4189,15 +4300,17 @@
       </c>
       <c r="H11" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I11" s="28">
         <f>IFERROR(IF(SUM(C11:G11)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C11:G11)), "")</f>
         <v/>
       </c>
-      <c r="J11" s="70" t="n">
-        <v/>
+      <c r="J11" s="70" t="inlineStr">
+        <is>
+          <t>تنزيل حديد</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" s="44">
@@ -4221,7 +4334,7 @@
       </c>
       <c r="H12" s="75" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I12" s="34">
@@ -4253,7 +4366,7 @@
       </c>
       <c r="H13" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I13" s="28">
@@ -4287,7 +4400,7 @@
       </c>
       <c r="H14" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I14" s="34">
@@ -4319,7 +4432,7 @@
       </c>
       <c r="H15" s="69" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I15" s="28">
@@ -4415,7 +4528,7 @@
       </c>
       <c r="H18" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I18" s="34">
@@ -4447,7 +4560,7 @@
       </c>
       <c r="H19" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I19" s="28">
@@ -4479,7 +4592,7 @@
       </c>
       <c r="H20" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I20" s="34">
@@ -4513,7 +4626,7 @@
       </c>
       <c r="H21" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I21" s="28">
@@ -4545,7 +4658,7 @@
       </c>
       <c r="H22" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I22" s="34">
@@ -4568,7 +4681,9 @@
       <c r="C23" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D23" s="68" t="n"/>
+      <c r="D23" s="68" t="n">
+        <v>3</v>
+      </c>
       <c r="E23" s="68" t="n"/>
       <c r="F23" s="68" t="n"/>
       <c r="G23" s="26">
@@ -4577,15 +4692,17 @@
       </c>
       <c r="H23" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I23" s="28">
         <f>IFERROR(IF(SUM(C23:G23)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C23:G23)), "")</f>
         <v/>
       </c>
-      <c r="J23" s="70" t="n">
-        <v/>
+      <c r="J23" s="70" t="inlineStr">
+        <is>
+          <t>عمل إضافي في المزرعة</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1" s="44">
@@ -4609,7 +4726,7 @@
       </c>
       <c r="H24" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I24" s="34">
@@ -4641,7 +4758,7 @@
       </c>
       <c r="H25" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I25" s="28">
@@ -4675,7 +4792,7 @@
       </c>
       <c r="H26" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I26" s="34">
@@ -4709,7 +4826,7 @@
       </c>
       <c r="H27" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I27" s="28">
@@ -4743,7 +4860,7 @@
       </c>
       <c r="H28" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I28" s="34">
@@ -4768,7 +4885,9 @@
       <c r="C29" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D29" s="68" t="n"/>
+      <c r="D29" s="68" t="n">
+        <v>2</v>
+      </c>
       <c r="E29" s="68" t="n"/>
       <c r="F29" s="68" t="n"/>
       <c r="G29" s="26">
@@ -4777,7 +4896,7 @@
       </c>
       <c r="H29" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I29" s="28">
@@ -4802,7 +4921,9 @@
       <c r="C30" s="72" t="n">
         <v>8</v>
       </c>
-      <c r="D30" s="71" t="n"/>
+      <c r="D30" s="71" t="n">
+        <v>2</v>
+      </c>
       <c r="E30" s="74" t="n"/>
       <c r="F30" s="74" t="n"/>
       <c r="G30" s="29">
@@ -4811,7 +4932,7 @@
       </c>
       <c r="H30" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I30" s="34">
@@ -4834,7 +4955,9 @@
       <c r="C31" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D31" s="68" t="n"/>
+      <c r="D31" s="68" t="n">
+        <v>2</v>
+      </c>
       <c r="E31" s="68" t="n"/>
       <c r="F31" s="68" t="n"/>
       <c r="G31" s="26">
@@ -4868,7 +4991,9 @@
       <c r="C32" s="72" t="n">
         <v>8</v>
       </c>
-      <c r="D32" s="71" t="n"/>
+      <c r="D32" s="71" t="n">
+        <v>2</v>
+      </c>
       <c r="E32" s="74" t="n"/>
       <c r="F32" s="74" t="n"/>
       <c r="G32" s="29">
@@ -4900,7 +5025,9 @@
       <c r="C33" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D33" s="68" t="n"/>
+      <c r="D33" s="68" t="n">
+        <v>1</v>
+      </c>
       <c r="E33" s="68" t="n"/>
       <c r="F33" s="68" t="n"/>
       <c r="G33" s="26">
@@ -4966,7 +5093,9 @@
       <c r="C35" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D35" s="68" t="n"/>
+      <c r="D35" s="68" t="n">
+        <v>2</v>
+      </c>
       <c r="E35" s="68" t="n"/>
       <c r="F35" s="68" t="n"/>
       <c r="G35" s="26">
@@ -4975,7 +5104,7 @@
       </c>
       <c r="H35" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I35" s="28">
@@ -4998,7 +5127,9 @@
       <c r="C36" s="72" t="n">
         <v>8</v>
       </c>
-      <c r="D36" s="74" t="n"/>
+      <c r="D36" s="74" t="n">
+        <v>2</v>
+      </c>
       <c r="E36" s="74" t="n"/>
       <c r="F36" s="74" t="n"/>
       <c r="G36" s="29" t="n"/>
@@ -5027,13 +5158,15 @@
       <c r="C37" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D37" s="68" t="n"/>
+      <c r="D37" s="68" t="n">
+        <v>2</v>
+      </c>
       <c r="E37" s="68" t="n"/>
       <c r="F37" s="68" t="n"/>
       <c r="G37" s="26" t="n"/>
       <c r="H37" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I37" s="28">
@@ -5411,7 +5544,7 @@
       </c>
       <c r="B4" s="58" t="inlineStr">
         <is>
-          <t>محمد ادريس عجب كل</t>
+          <t xml:space="preserve"> محمد عويس شير اكبر</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -5511,7 +5644,7 @@
       <c r="G7" s="26" t="n"/>
       <c r="H7" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I7" s="28">
@@ -5543,7 +5676,7 @@
       </c>
       <c r="H8" s="75" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I8" s="34">
@@ -5575,7 +5708,7 @@
       </c>
       <c r="H9" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I9" s="28">
@@ -5607,7 +5740,7 @@
       </c>
       <c r="H10" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I10" s="34">
@@ -5630,9 +5763,7 @@
       <c r="C11" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="68" t="n">
-        <v>3</v>
-      </c>
+      <c r="D11" s="68" t="n"/>
       <c r="E11" s="68" t="n"/>
       <c r="F11" s="68" t="n"/>
       <c r="G11" s="26">
@@ -5641,17 +5772,15 @@
       </c>
       <c r="H11" s="69" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I11" s="28">
         <f>IFERROR(IF(SUM(C11:G11)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C11:G11)), "")</f>
         <v/>
       </c>
-      <c r="J11" s="70" t="inlineStr">
-        <is>
-          <t>تنزيل حديد</t>
-        </is>
+      <c r="J11" s="70" t="n">
+        <v/>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" s="44">
@@ -5675,7 +5804,7 @@
       </c>
       <c r="H12" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I12" s="34">
@@ -5707,7 +5836,7 @@
       </c>
       <c r="H13" s="69" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I13" s="28">
@@ -5741,7 +5870,7 @@
       </c>
       <c r="H14" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I14" s="34">
@@ -5773,7 +5902,7 @@
       </c>
       <c r="H15" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I15" s="28">
@@ -5805,7 +5934,7 @@
       </c>
       <c r="H16" s="75" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I16" s="34">
@@ -5837,7 +5966,7 @@
       </c>
       <c r="H17" s="69" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I17" s="28">
@@ -5967,7 +6096,7 @@
       </c>
       <c r="H21" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I21" s="28">
@@ -5999,7 +6128,7 @@
       </c>
       <c r="H22" s="75" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I22" s="34">
@@ -6022,9 +6151,7 @@
       <c r="C23" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D23" s="68" t="n">
-        <v>3</v>
-      </c>
+      <c r="D23" s="68" t="n"/>
       <c r="E23" s="68" t="n"/>
       <c r="F23" s="68" t="n"/>
       <c r="G23" s="26">
@@ -6033,17 +6160,15 @@
       </c>
       <c r="H23" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I23" s="28">
         <f>IFERROR(IF(SUM(C23:G23)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C23:G23)), "")</f>
         <v/>
       </c>
-      <c r="J23" s="70" t="inlineStr">
-        <is>
-          <t>عمل إضافي في المزرعة</t>
-        </is>
+      <c r="J23" s="70" t="n">
+        <v/>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1" s="44">
@@ -6067,7 +6192,7 @@
       </c>
       <c r="H24" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I24" s="34">
@@ -6099,7 +6224,7 @@
       </c>
       <c r="H25" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I25" s="28">
@@ -6133,7 +6258,7 @@
       </c>
       <c r="H26" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I26" s="34">
@@ -6167,7 +6292,7 @@
       </c>
       <c r="H27" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I27" s="28">
@@ -6201,7 +6326,7 @@
       </c>
       <c r="H28" s="75" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I28" s="34">
@@ -6350,8 +6475,10 @@
         <f>IFERROR(IF(SUM(C32:G32)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C32:G32)), "")</f>
         <v/>
       </c>
-      <c r="J32" s="70" t="n">
-        <v/>
+      <c r="J32" s="70" t="inlineStr">
+        <is>
+          <t>لسا مريض</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1" s="44">
@@ -6360,15 +6487,13 @@
       </c>
       <c r="B33" s="68" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="C33" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D33" s="68" t="n">
-        <v>1</v>
-      </c>
+      <c r="D33" s="68" t="n"/>
       <c r="E33" s="68" t="n"/>
       <c r="F33" s="68" t="n"/>
       <c r="G33" s="26">
@@ -6384,8 +6509,10 @@
         <f>IFERROR(IF(SUM(C33:G33)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C33:G33)), "")</f>
         <v/>
       </c>
-      <c r="J33" s="70" t="n">
-        <v/>
+      <c r="J33" s="70" t="inlineStr">
+        <is>
+          <t>غياب مرضي</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1" s="44">
@@ -6428,15 +6555,13 @@
       </c>
       <c r="B35" s="68" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="C35" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D35" s="68" t="n">
-        <v>2</v>
-      </c>
+      <c r="D35" s="68" t="n"/>
       <c r="E35" s="68" t="n"/>
       <c r="F35" s="68" t="n"/>
       <c r="G35" s="26">
@@ -6452,8 +6577,10 @@
         <f>IFERROR(IF(SUM(C35:G35)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C35:G35)), "")</f>
         <v/>
       </c>
-      <c r="J35" s="70" t="n">
-        <v/>
+      <c r="J35" s="70" t="inlineStr">
+        <is>
+          <t>اجازة مرضية</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1" s="44">
@@ -6462,15 +6589,13 @@
       </c>
       <c r="B36" s="79" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="C36" s="72" t="n">
         <v>8</v>
       </c>
-      <c r="D36" s="74" t="n">
-        <v>2</v>
-      </c>
+      <c r="D36" s="74" t="n"/>
       <c r="E36" s="74" t="n"/>
       <c r="F36" s="74" t="n"/>
       <c r="G36" s="29" t="n"/>
@@ -6483,8 +6608,10 @@
         <f>IFERROR(IF(SUM(C36:G36)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C36:G36)), "")</f>
         <v/>
       </c>
-      <c r="J36" s="70" t="n">
-        <v/>
+      <c r="J36" s="70" t="inlineStr">
+        <is>
+          <t>لسا مريض</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1" s="44">
@@ -6493,15 +6620,13 @@
       </c>
       <c r="B37" s="68" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="C37" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D37" s="68" t="n">
-        <v>2</v>
-      </c>
+      <c r="D37" s="68" t="n"/>
       <c r="E37" s="68" t="n"/>
       <c r="F37" s="68" t="n"/>
       <c r="G37" s="26" t="n"/>
@@ -6514,8 +6639,10 @@
         <f>IFERROR(IF(SUM(C37:G37)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C37:G37)), "")</f>
         <v/>
       </c>
-      <c r="J37" s="70" t="n">
-        <v/>
+      <c r="J37" s="70" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1" s="44">
@@ -6853,7 +6980,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -6885,7 +7012,7 @@
       </c>
       <c r="B4" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> محمد عويس شير اكبر</t>
+          <t>ميلكامو مولا بيليو</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -7492,7 +7619,9 @@
       <c r="C23" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D23" s="68" t="n"/>
+      <c r="D23" s="68" t="n">
+        <v>3</v>
+      </c>
       <c r="E23" s="68" t="n"/>
       <c r="F23" s="68" t="n"/>
       <c r="G23" s="26">
@@ -7508,8 +7637,10 @@
         <f>IFERROR(IF(SUM(C23:G23)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C23:G23)), "")</f>
         <v/>
       </c>
-      <c r="J23" s="70" t="n">
-        <v/>
+      <c r="J23" s="70" t="inlineStr">
+        <is>
+          <t>عمل إضافي في سالم</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1" s="44">
@@ -7816,10 +7947,8 @@
         <f>IFERROR(IF(SUM(C32:G32)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C32:G32)), "")</f>
         <v/>
       </c>
-      <c r="J32" s="70" t="inlineStr">
-        <is>
-          <t>لسا مريض</t>
-        </is>
+      <c r="J32" s="70" t="n">
+        <v/>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1" s="44">
@@ -7828,13 +7957,15 @@
       </c>
       <c r="B33" s="68" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C33" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D33" s="68" t="n"/>
+      <c r="D33" s="68" t="n">
+        <v>1</v>
+      </c>
       <c r="E33" s="68" t="n"/>
       <c r="F33" s="68" t="n"/>
       <c r="G33" s="26">
@@ -7850,10 +7981,8 @@
         <f>IFERROR(IF(SUM(C33:G33)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C33:G33)), "")</f>
         <v/>
       </c>
-      <c r="J33" s="70" t="inlineStr">
-        <is>
-          <t>غياب مرضي</t>
-        </is>
+      <c r="J33" s="70" t="n">
+        <v/>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1" s="44">
@@ -7896,13 +8025,15 @@
       </c>
       <c r="B35" s="68" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C35" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D35" s="68" t="n"/>
+      <c r="D35" s="68" t="n">
+        <v>2</v>
+      </c>
       <c r="E35" s="68" t="n"/>
       <c r="F35" s="68" t="n"/>
       <c r="G35" s="26">
@@ -7918,10 +8049,8 @@
         <f>IFERROR(IF(SUM(C35:G35)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C35:G35)), "")</f>
         <v/>
       </c>
-      <c r="J35" s="70" t="inlineStr">
-        <is>
-          <t>اجازة مرضية</t>
-        </is>
+      <c r="J35" s="70" t="n">
+        <v/>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1" s="44">
@@ -7930,25 +8059,29 @@
       </c>
       <c r="B36" s="79" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C36" s="72" t="n"/>
-      <c r="D36" s="74" t="n"/>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C36" s="72" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" s="74" t="n">
+        <v>2</v>
+      </c>
       <c r="E36" s="74" t="n"/>
       <c r="F36" s="74" t="n"/>
       <c r="G36" s="29" t="n"/>
-      <c r="H36" s="75" t="n">
-        <v/>
+      <c r="H36" s="75" t="inlineStr">
+        <is>
+          <t>Salem Al Zaabi</t>
+        </is>
       </c>
       <c r="I36" s="34">
         <f>IFERROR(IF(SUM(C36:G36)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C36:G36)), "")</f>
         <v/>
       </c>
-      <c r="J36" s="70" t="inlineStr">
-        <is>
-          <t>لسا مريض</t>
-        </is>
+      <c r="J36" s="70" t="n">
+        <v/>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1" s="44">
@@ -7957,25 +8090,29 @@
       </c>
       <c r="B37" s="68" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C37" s="68" t="n"/>
-      <c r="D37" s="68" t="n"/>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C37" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" s="68" t="n">
+        <v>2</v>
+      </c>
       <c r="E37" s="68" t="n"/>
       <c r="F37" s="68" t="n"/>
       <c r="G37" s="26" t="n"/>
-      <c r="H37" s="69" t="n">
-        <v/>
+      <c r="H37" s="69" t="inlineStr">
+        <is>
+          <t>Salem Al Zaabi</t>
+        </is>
       </c>
       <c r="I37" s="28">
         <f>IFERROR(IF(SUM(C37:G37)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C37:G37)), "")</f>
         <v/>
       </c>
-      <c r="J37" s="70" t="inlineStr">
-        <is>
-          <t>لسا مريض</t>
-        </is>
+      <c r="J37" s="70" t="n">
+        <v/>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1" s="44">
@@ -8313,7 +8450,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -8345,7 +8482,7 @@
       </c>
       <c r="B4" s="58" t="inlineStr">
         <is>
-          <t>ميلكامو مولا بيليو</t>
+          <t>امارى ميسقى وبيتو</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -8605,7 +8742,7 @@
       </c>
       <c r="H12" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I12" s="34">
@@ -8637,7 +8774,7 @@
       </c>
       <c r="H13" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I13" s="28">
@@ -8671,7 +8808,7 @@
       </c>
       <c r="H14" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I14" s="34">
@@ -8703,7 +8840,7 @@
       </c>
       <c r="H15" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I15" s="28">
@@ -8735,7 +8872,7 @@
       </c>
       <c r="H16" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I16" s="34">
@@ -8767,7 +8904,7 @@
       </c>
       <c r="H17" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I17" s="28">
@@ -8799,7 +8936,7 @@
       </c>
       <c r="H18" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I18" s="34">
@@ -8831,7 +8968,7 @@
       </c>
       <c r="H19" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I19" s="28">
@@ -8863,7 +9000,7 @@
       </c>
       <c r="H20" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I20" s="34">
@@ -8897,7 +9034,7 @@
       </c>
       <c r="H21" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I21" s="28">
@@ -8929,7 +9066,7 @@
       </c>
       <c r="H22" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I22" s="34">
@@ -8997,7 +9134,7 @@
       </c>
       <c r="H24" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I24" s="34">
@@ -9029,7 +9166,7 @@
       </c>
       <c r="H25" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I25" s="28">
@@ -9063,7 +9200,7 @@
       </c>
       <c r="H26" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I26" s="34">
@@ -9097,7 +9234,7 @@
       </c>
       <c r="H27" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I27" s="28">
@@ -9131,7 +9268,7 @@
       </c>
       <c r="H28" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I28" s="34">
@@ -9167,7 +9304,7 @@
       </c>
       <c r="H29" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I29" s="28">
@@ -9203,7 +9340,7 @@
       </c>
       <c r="H30" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I30" s="34">
@@ -9375,7 +9512,7 @@
       </c>
       <c r="H35" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I35" s="28">
@@ -9406,7 +9543,7 @@
       <c r="G36" s="29" t="n"/>
       <c r="H36" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I36" s="34">
@@ -9437,7 +9574,7 @@
       <c r="G37" s="26" t="n"/>
       <c r="H37" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I37" s="28">
@@ -9783,7 +9920,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -9815,7 +9952,7 @@
       </c>
       <c r="B4" s="58" t="inlineStr">
         <is>
-          <t>امارى ميسقى وبيتو</t>
+          <t>ابابو موجيس نيجيس</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -9947,7 +10084,7 @@
       </c>
       <c r="H8" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I8" s="34">
@@ -10075,7 +10212,7 @@
       </c>
       <c r="H12" s="75" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I12" s="34">
@@ -10107,7 +10244,7 @@
       </c>
       <c r="H13" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I13" s="28">
@@ -10269,7 +10406,7 @@
       </c>
       <c r="H18" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I18" s="34">
@@ -10301,7 +10438,7 @@
       </c>
       <c r="H19" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I19" s="28">
@@ -10333,7 +10470,7 @@
       </c>
       <c r="H20" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I20" s="34">
@@ -11253,7 +11390,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1100</t>
         </is>
       </c>
     </row>
@@ -11285,7 +11422,7 @@
       </c>
       <c r="B4" s="58" t="inlineStr">
         <is>
-          <t>ابابو موجيس نيجيس</t>
+          <t>باجر انجلال شارهان</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -11385,7 +11522,7 @@
       <c r="G7" s="26" t="n"/>
       <c r="H7" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I7" s="28">
@@ -11417,7 +11554,7 @@
       </c>
       <c r="H8" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I8" s="34">
@@ -11449,7 +11586,7 @@
       </c>
       <c r="H9" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I9" s="28">
@@ -11481,7 +11618,7 @@
       </c>
       <c r="H10" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I10" s="34">
@@ -11504,7 +11641,9 @@
       <c r="C11" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="68" t="n"/>
+      <c r="D11" s="68" t="n">
+        <v>3</v>
+      </c>
       <c r="E11" s="68" t="n"/>
       <c r="F11" s="68" t="n"/>
       <c r="G11" s="26">
@@ -11513,15 +11652,17 @@
       </c>
       <c r="H11" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I11" s="28">
         <f>IFERROR(IF(SUM(C11:G11)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C11:G11)), "")</f>
         <v/>
       </c>
-      <c r="J11" s="70" t="n">
-        <v/>
+      <c r="J11" s="70" t="inlineStr">
+        <is>
+          <t>تنزيل حديد</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" s="44">
@@ -11536,7 +11677,9 @@
       <c r="C12" s="72" t="n">
         <v>8</v>
       </c>
-      <c r="D12" s="71" t="n"/>
+      <c r="D12" s="71" t="n">
+        <v>3</v>
+      </c>
       <c r="E12" s="73" t="n"/>
       <c r="F12" s="74" t="n"/>
       <c r="G12" s="29">
@@ -11545,15 +11688,17 @@
       </c>
       <c r="H12" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I12" s="34">
         <f>IFERROR(IF(SUM(C12:G12)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C12:G12)), "")</f>
         <v/>
       </c>
-      <c r="J12" s="70" t="n">
-        <v/>
+      <c r="J12" s="70" t="inlineStr">
+        <is>
+          <t>تنزيل طابوق</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" s="44">
@@ -11569,7 +11714,9 @@
         <v>8</v>
       </c>
       <c r="D13" s="68" t="n"/>
-      <c r="E13" s="68" t="n"/>
+      <c r="E13" s="68" t="n">
+        <v>3</v>
+      </c>
       <c r="F13" s="68" t="n"/>
       <c r="G13" s="26">
         <f>IF(B13="SL","SL","")</f>
@@ -11577,7 +11724,7 @@
       </c>
       <c r="H13" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I13" s="28">
@@ -11586,7 +11733,7 @@
       </c>
       <c r="J13" s="70" t="inlineStr">
         <is>
-          <t>Weekend</t>
+          <t>Weekend تنزيل طابوق</t>
         </is>
       </c>
     </row>
@@ -11611,7 +11758,7 @@
       </c>
       <c r="H14" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I14" s="34">
@@ -11643,7 +11790,7 @@
       </c>
       <c r="H15" s="69" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I15" s="28">
@@ -11707,7 +11854,7 @@
       </c>
       <c r="H17" s="69" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I17" s="28">
@@ -11739,7 +11886,7 @@
       </c>
       <c r="H18" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I18" s="34">
@@ -11771,7 +11918,7 @@
       </c>
       <c r="H19" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I19" s="28">
@@ -11803,7 +11950,7 @@
       </c>
       <c r="H20" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I20" s="34">
@@ -11837,7 +11984,7 @@
       </c>
       <c r="H21" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I21" s="28">
@@ -11869,7 +12016,7 @@
       </c>
       <c r="H22" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I22" s="34">
@@ -11903,7 +12050,7 @@
       </c>
       <c r="H23" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I23" s="28">
@@ -11912,7 +12059,7 @@
       </c>
       <c r="J23" s="70" t="inlineStr">
         <is>
-          <t>عمل إضافي في سالم</t>
+          <t>عمل إضافي في المزرعة</t>
         </is>
       </c>
     </row>
@@ -11937,7 +12084,7 @@
       </c>
       <c r="H24" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I24" s="34">
@@ -11969,7 +12116,7 @@
       </c>
       <c r="H25" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I25" s="28">
@@ -12003,7 +12150,7 @@
       </c>
       <c r="H26" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I26" s="34">
@@ -12037,7 +12184,7 @@
       </c>
       <c r="H27" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I27" s="28">
@@ -12071,7 +12218,7 @@
       </c>
       <c r="H28" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I28" s="34">
@@ -12107,7 +12254,7 @@
       </c>
       <c r="H29" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I29" s="28">
@@ -12143,7 +12290,7 @@
       </c>
       <c r="H30" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I30" s="34">
@@ -12247,7 +12394,7 @@
       </c>
       <c r="H33" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I33" s="28">
@@ -12315,7 +12462,7 @@
       </c>
       <c r="H35" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I35" s="28">
@@ -12723,1486 +12870,6 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>1100</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="35.4" customHeight="1" s="44">
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>نهاية الشهر</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>46112</v>
-      </c>
-      <c r="G3" s="56" t="n"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الراتب اليومي : </t>
-        </is>
-      </c>
-      <c r="I3" s="5">
-        <f>I2/DAY(EOMONTH(F3, 0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="55.2" customHeight="1" s="44">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>اسم الموظف</t>
-        </is>
-      </c>
-      <c r="B4" s="58" t="inlineStr">
-        <is>
-          <t>باجر انجلال شارهان</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>الشهر</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="G4" s="56" t="n"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>ساعة العامل :</t>
-        </is>
-      </c>
-      <c r="I4" s="60">
-        <f>I3/8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="17.4" customHeight="1" s="44">
-      <c r="A5" s="52" t="n"/>
-      <c r="B5" s="53" t="n"/>
-      <c r="C5" s="53" t="n"/>
-      <c r="D5" s="53" t="n"/>
-      <c r="E5" s="53" t="n"/>
-      <c r="F5" s="53" t="n"/>
-      <c r="G5" s="53" t="n"/>
-      <c r="H5" s="53" t="n"/>
-      <c r="I5" s="53" t="n"/>
-    </row>
-    <row r="6" ht="75.59999999999999" customHeight="1" s="44">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>الحضور</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساعات العمل </t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساعات العمل الإضافية </t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>ساعات العمل خلال الإجازة</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساعات العمل بالمناسبات الرسمية </t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>إجازة مرضية</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>المشروع</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>الاجمالي</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1" s="44">
-      <c r="A7" s="61" t="n">
-        <v>46082</v>
-      </c>
-      <c r="B7" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C7" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D7" s="68" t="n"/>
-      <c r="E7" s="68" t="n"/>
-      <c r="F7" s="68" t="n"/>
-      <c r="G7" s="26" t="n"/>
-      <c r="H7" s="69" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
-      </c>
-      <c r="I7" s="28">
-        <f>IFERROR(IF(SUM(C7:G7)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C7:G7)), "")</f>
-        <v/>
-      </c>
-      <c r="J7" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1" s="44">
-      <c r="A8" s="62" t="n">
-        <v>46083</v>
-      </c>
-      <c r="B8" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C8" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" s="71" t="n"/>
-      <c r="E8" s="73" t="n"/>
-      <c r="F8" s="74" t="n"/>
-      <c r="G8" s="29">
-        <f>IF(B8="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H8" s="75" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
-      </c>
-      <c r="I8" s="34">
-        <f>IFERROR(IF(SUM(C8:G8)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C8:G8)), "")</f>
-        <v/>
-      </c>
-      <c r="J8" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1" s="44">
-      <c r="A9" s="61" t="n">
-        <v>46084</v>
-      </c>
-      <c r="B9" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C9" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D9" s="68" t="n"/>
-      <c r="E9" s="68" t="n"/>
-      <c r="F9" s="68" t="n"/>
-      <c r="G9" s="26">
-        <f>IF(B9="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H9" s="69" t="inlineStr">
-        <is>
-          <t>Farm 826</t>
-        </is>
-      </c>
-      <c r="I9" s="28">
-        <f>IFERROR(IF(SUM(C9:G9)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C9:G9)), "")</f>
-        <v/>
-      </c>
-      <c r="J9" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1" s="44">
-      <c r="A10" s="62" t="n">
-        <v>46085</v>
-      </c>
-      <c r="B10" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C10" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" s="71" t="n"/>
-      <c r="E10" s="73" t="n"/>
-      <c r="F10" s="74" t="n"/>
-      <c r="G10" s="29">
-        <f>IF(B10="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H10" s="75" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
-      </c>
-      <c r="I10" s="34">
-        <f>IFERROR(IF(SUM(C10:G10)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C10:G10)), "")</f>
-        <v/>
-      </c>
-      <c r="J10" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" s="44">
-      <c r="A11" s="61" t="n">
-        <v>46086</v>
-      </c>
-      <c r="B11" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C11" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="68" t="n"/>
-      <c r="F11" s="68" t="n"/>
-      <c r="G11" s="26">
-        <f>IF(B11="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H11" s="69" t="inlineStr">
-        <is>
-          <t>Waleed Al Amari</t>
-        </is>
-      </c>
-      <c r="I11" s="28">
-        <f>IFERROR(IF(SUM(C11:G11)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C11:G11)), "")</f>
-        <v/>
-      </c>
-      <c r="J11" s="70" t="inlineStr">
-        <is>
-          <t>تنزيل حديد</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1" s="44">
-      <c r="A12" s="62" t="n">
-        <v>46087</v>
-      </c>
-      <c r="B12" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C12" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" s="71" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="73" t="n"/>
-      <c r="F12" s="74" t="n"/>
-      <c r="G12" s="29">
-        <f>IF(B12="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H12" s="75" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
-      </c>
-      <c r="I12" s="34">
-        <f>IFERROR(IF(SUM(C12:G12)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C12:G12)), "")</f>
-        <v/>
-      </c>
-      <c r="J12" s="70" t="inlineStr">
-        <is>
-          <t>تنزيل طابوق</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1" s="44">
-      <c r="A13" s="62" t="n">
-        <v>46088</v>
-      </c>
-      <c r="B13" s="76" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="C13" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" s="68" t="n"/>
-      <c r="F13" s="68" t="n"/>
-      <c r="G13" s="26">
-        <f>IF(B13="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H13" s="69" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
-      </c>
-      <c r="I13" s="28">
-        <f>IFERROR(IF(SUM(C13:G13)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C13:G13)), "")</f>
-        <v/>
-      </c>
-      <c r="J13" s="70" t="inlineStr">
-        <is>
-          <t>Weekend تنزيل طابوق</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1" s="44">
-      <c r="A14" s="62" t="n">
-        <v>46089</v>
-      </c>
-      <c r="B14" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C14" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" s="71" t="n"/>
-      <c r="E14" s="74" t="n"/>
-      <c r="F14" s="74" t="n"/>
-      <c r="G14" s="29">
-        <f>IF(B14="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H14" s="75" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
-      </c>
-      <c r="I14" s="34">
-        <f>IFERROR(IF(SUM(C14:G14)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C14:G14)), "")</f>
-        <v/>
-      </c>
-      <c r="J14" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1" s="44">
-      <c r="A15" s="61" t="n">
-        <v>46090</v>
-      </c>
-      <c r="B15" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C15" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" s="68" t="n"/>
-      <c r="E15" s="68" t="n"/>
-      <c r="F15" s="68" t="n"/>
-      <c r="G15" s="26">
-        <f>IF(B15="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H15" s="69" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
-      </c>
-      <c r="I15" s="28">
-        <f>IFERROR(IF(SUM(C15:G15)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C15:G15)), "")</f>
-        <v/>
-      </c>
-      <c r="J15" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1" s="44">
-      <c r="A16" s="62" t="n">
-        <v>46091</v>
-      </c>
-      <c r="B16" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C16" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D16" s="71" t="n"/>
-      <c r="E16" s="74" t="n"/>
-      <c r="F16" s="74" t="n"/>
-      <c r="G16" s="29">
-        <f>IF(B16="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H16" s="75" t="inlineStr">
-        <is>
-          <t>Waleed Al Amari</t>
-        </is>
-      </c>
-      <c r="I16" s="34">
-        <f>IFERROR(IF(SUM(C16:G16)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C16:G16)), "")</f>
-        <v/>
-      </c>
-      <c r="J16" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1" s="44">
-      <c r="A17" s="61" t="n">
-        <v>46092</v>
-      </c>
-      <c r="B17" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C17" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D17" s="68" t="n"/>
-      <c r="E17" s="68" t="n"/>
-      <c r="F17" s="68" t="n"/>
-      <c r="G17" s="26">
-        <f>IF(B17="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H17" s="69" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
-      </c>
-      <c r="I17" s="28">
-        <f>IFERROR(IF(SUM(C17:G17)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C17:G17)), "")</f>
-        <v/>
-      </c>
-      <c r="J17" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1" s="44">
-      <c r="A18" s="62" t="n">
-        <v>46093</v>
-      </c>
-      <c r="B18" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C18" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" s="71" t="n"/>
-      <c r="E18" s="74" t="n"/>
-      <c r="F18" s="74" t="n"/>
-      <c r="G18" s="29">
-        <f>IF(B18="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H18" s="75" t="inlineStr">
-        <is>
-          <t>Salem Al Zaabi</t>
-        </is>
-      </c>
-      <c r="I18" s="34">
-        <f>IFERROR(IF(SUM(C18:G18)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C18:G18)), "")</f>
-        <v/>
-      </c>
-      <c r="J18" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1" s="44">
-      <c r="A19" s="61" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B19" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C19" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" s="68" t="n"/>
-      <c r="E19" s="68" t="n"/>
-      <c r="F19" s="68" t="n"/>
-      <c r="G19" s="26">
-        <f>IF(B19="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H19" s="69" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
-      </c>
-      <c r="I19" s="28">
-        <f>IFERROR(IF(SUM(C19:G19)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C19:G19)), "")</f>
-        <v/>
-      </c>
-      <c r="J19" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1" s="44">
-      <c r="A20" s="62" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B20" s="76" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="C20" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D20" s="71" t="n"/>
-      <c r="E20" s="74" t="n"/>
-      <c r="F20" s="74" t="n"/>
-      <c r="G20" s="29">
-        <f>IF(B20="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H20" s="75" t="inlineStr">
-        <is>
-          <t>Salem Al Zaabi</t>
-        </is>
-      </c>
-      <c r="I20" s="34">
-        <f>IFERROR(IF(SUM(C20:G20)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C20:G20)), "")</f>
-        <v/>
-      </c>
-      <c r="J20" s="70" t="inlineStr">
-        <is>
-          <t>Weekend</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1" s="44">
-      <c r="A21" s="61" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B21" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C21" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D21" s="68" t="n"/>
-      <c r="E21" s="68" t="n"/>
-      <c r="F21" s="68" t="n"/>
-      <c r="G21" s="26">
-        <f>IF(B21="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H21" s="69" t="inlineStr">
-        <is>
-          <t>Farm 826</t>
-        </is>
-      </c>
-      <c r="I21" s="28">
-        <f>IFERROR(IF(SUM(C21:G21)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C21:G21)), "")</f>
-        <v/>
-      </c>
-      <c r="J21" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1" s="44">
-      <c r="A22" s="62" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B22" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C22" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D22" s="71" t="n"/>
-      <c r="E22" s="74" t="n"/>
-      <c r="F22" s="74" t="n"/>
-      <c r="G22" s="29">
-        <f>IF(B21="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H22" s="75" t="inlineStr">
-        <is>
-          <t>Farm 826</t>
-        </is>
-      </c>
-      <c r="I22" s="34">
-        <f>IFERROR(IF(SUM(C21:G21)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C21:G21)), "")</f>
-        <v/>
-      </c>
-      <c r="J22" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1" s="44">
-      <c r="A23" s="61" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B23" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C23" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D23" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" s="68" t="n"/>
-      <c r="F23" s="68" t="n"/>
-      <c r="G23" s="26">
-        <f>IF(B23="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H23" s="69" t="inlineStr">
-        <is>
-          <t>Farm 826</t>
-        </is>
-      </c>
-      <c r="I23" s="28">
-        <f>IFERROR(IF(SUM(C23:G23)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C23:G23)), "")</f>
-        <v/>
-      </c>
-      <c r="J23" s="70" t="inlineStr">
-        <is>
-          <t>عمل إضافي في المزرعة</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1" s="44">
-      <c r="A24" s="62" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B24" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C24" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D24" s="71" t="n"/>
-      <c r="E24" s="74" t="n"/>
-      <c r="F24" s="74" t="n"/>
-      <c r="G24" s="29">
-        <f>IF(B24="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H24" s="75" t="inlineStr">
-        <is>
-          <t>Farm 826</t>
-        </is>
-      </c>
-      <c r="I24" s="34">
-        <f>IFERROR(IF(SUM(C24:G24)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C24:G24)), "")</f>
-        <v/>
-      </c>
-      <c r="J24" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1" s="44">
-      <c r="A25" s="61" t="n">
-        <v>46100</v>
-      </c>
-      <c r="B25" s="77" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C25" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D25" s="68" t="n"/>
-      <c r="E25" s="68" t="n"/>
-      <c r="F25" s="68" t="n"/>
-      <c r="G25" s="26">
-        <f>IF(B25="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H25" s="69" t="inlineStr">
-        <is>
-          <t>Farm 826</t>
-        </is>
-      </c>
-      <c r="I25" s="28">
-        <f>IFERROR(IF(SUM(C25:G25)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C25:G25)), "")</f>
-        <v/>
-      </c>
-      <c r="J25" s="70" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1" s="44">
-      <c r="A26" s="62" t="n">
-        <v>46101</v>
-      </c>
-      <c r="B26" s="77" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C26" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D26" s="71" t="n"/>
-      <c r="E26" s="74" t="n"/>
-      <c r="F26" s="74" t="n"/>
-      <c r="G26" s="29">
-        <f>IF(B26="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H26" s="75" t="inlineStr">
-        <is>
-          <t>Farm 826</t>
-        </is>
-      </c>
-      <c r="I26" s="34">
-        <f>IFERROR(IF(SUM(C26:G26)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C26:G26)), "")</f>
-        <v/>
-      </c>
-      <c r="J26" s="70" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1" s="44">
-      <c r="A27" s="61" t="n">
-        <v>46102</v>
-      </c>
-      <c r="B27" s="77" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C27" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D27" s="68" t="n"/>
-      <c r="E27" s="68" t="n"/>
-      <c r="F27" s="68" t="n"/>
-      <c r="G27" s="26">
-        <f>IF(B27="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H27" s="69" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
-      </c>
-      <c r="I27" s="28">
-        <f>IFERROR(IF(SUM(C27:G27)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C27:G27)), "")</f>
-        <v/>
-      </c>
-      <c r="J27" s="70" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1" s="44">
-      <c r="A28" s="62" t="n">
-        <v>46103</v>
-      </c>
-      <c r="B28" s="77" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C28" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D28" s="71" t="n"/>
-      <c r="E28" s="74" t="n"/>
-      <c r="F28" s="74" t="n"/>
-      <c r="G28" s="29">
-        <f>IF(B28="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H28" s="75" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
-      </c>
-      <c r="I28" s="34">
-        <f>IFERROR(IF(SUM(C28:G28)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C28:G28)), "")</f>
-        <v/>
-      </c>
-      <c r="J28" s="70" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1" s="44">
-      <c r="A29" s="61" t="n">
-        <v>46104</v>
-      </c>
-      <c r="B29" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C29" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D29" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" s="68" t="n"/>
-      <c r="F29" s="68" t="n"/>
-      <c r="G29" s="26">
-        <f>IF(B29="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H29" s="69" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
-      </c>
-      <c r="I29" s="28">
-        <f>IFERROR(IF(SUM(C29:G29)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C29:G29)), "")</f>
-        <v/>
-      </c>
-      <c r="J29" s="70" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1" s="44">
-      <c r="A30" s="62" t="n">
-        <v>46105</v>
-      </c>
-      <c r="B30" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C30" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D30" s="71" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" s="74" t="n"/>
-      <c r="F30" s="74" t="n"/>
-      <c r="G30" s="29">
-        <f>IF(B30="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H30" s="75" t="inlineStr">
-        <is>
-          <t>Farm 826</t>
-        </is>
-      </c>
-      <c r="I30" s="34">
-        <f>IFERROR(IF(SUM(C30:G30)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C30:G30)), "")</f>
-        <v/>
-      </c>
-      <c r="J30" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1" s="44">
-      <c r="A31" s="61" t="n">
-        <v>46106</v>
-      </c>
-      <c r="B31" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C31" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D31" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" s="68" t="n"/>
-      <c r="F31" s="68" t="n"/>
-      <c r="G31" s="26">
-        <f>IF(B31="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H31" s="69" t="inlineStr">
-        <is>
-          <t>Salem Al Zaabi</t>
-        </is>
-      </c>
-      <c r="I31" s="28">
-        <f>IFERROR(IF(SUM(C31:G31)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C31:G31)), "")</f>
-        <v/>
-      </c>
-      <c r="J31" s="70" t="inlineStr">
-        <is>
-          <t>Weekend</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1" s="44">
-      <c r="A32" s="62" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B32" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C32" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D32" s="71" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" s="74" t="n"/>
-      <c r="F32" s="74" t="n"/>
-      <c r="G32" s="29">
-        <f>IF(B32="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H32" s="75" t="inlineStr">
-        <is>
-          <t>Salem Al Zaabi</t>
-        </is>
-      </c>
-      <c r="I32" s="34">
-        <f>IFERROR(IF(SUM(C32:G32)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C32:G32)), "")</f>
-        <v/>
-      </c>
-      <c r="J32" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="32" customHeight="1" s="44">
-      <c r="A33" s="61" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B33" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C33" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D33" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="68" t="n"/>
-      <c r="F33" s="68" t="n"/>
-      <c r="G33" s="26">
-        <f>IF(B33="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H33" s="69" t="inlineStr">
-        <is>
-          <t>Waleed Al Amari</t>
-        </is>
-      </c>
-      <c r="I33" s="28">
-        <f>IFERROR(IF(SUM(C33:G33)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C33:G33)), "")</f>
-        <v/>
-      </c>
-      <c r="J33" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="32" customHeight="1" s="44">
-      <c r="A34" s="62" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B34" s="78" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="C34" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D34" s="74" t="n"/>
-      <c r="E34" s="74" t="n"/>
-      <c r="F34" s="74" t="n"/>
-      <c r="G34" s="29">
-        <f>IF(B34="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H34" s="75" t="inlineStr">
-        <is>
-          <t>Salem Al Zaabi</t>
-        </is>
-      </c>
-      <c r="I34" s="34">
-        <f>IFERROR(IF(SUM(C34:G34)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C34:G34)), "")</f>
-        <v/>
-      </c>
-      <c r="J34" s="70" t="inlineStr">
-        <is>
-          <t>Weekend</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="32" customHeight="1" s="44">
-      <c r="A35" s="61" t="n">
-        <v>46110</v>
-      </c>
-      <c r="B35" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C35" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D35" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" s="68" t="n"/>
-      <c r="F35" s="68" t="n"/>
-      <c r="G35" s="26">
-        <f>IF(B35="SL","SL","")</f>
-        <v/>
-      </c>
-      <c r="H35" s="69" t="inlineStr">
-        <is>
-          <t>Waleed Al Amari</t>
-        </is>
-      </c>
-      <c r="I35" s="28">
-        <f>IFERROR(IF(SUM(C35:G35)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C35:G35)), "")</f>
-        <v/>
-      </c>
-      <c r="J35" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="32" customHeight="1" s="44">
-      <c r="A36" s="62" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B36" s="79" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C36" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D36" s="74" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" s="74" t="n"/>
-      <c r="F36" s="74" t="n"/>
-      <c r="G36" s="29" t="n"/>
-      <c r="H36" s="75" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
-      </c>
-      <c r="I36" s="34">
-        <f>IFERROR(IF(SUM(C36:G36)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C36:G36)), "")</f>
-        <v/>
-      </c>
-      <c r="J36" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1" s="44">
-      <c r="A37" s="61" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B37" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C37" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D37" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" s="68" t="n"/>
-      <c r="F37" s="68" t="n"/>
-      <c r="G37" s="26" t="n"/>
-      <c r="H37" s="69" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
-      </c>
-      <c r="I37" s="28">
-        <f>IFERROR(IF(SUM(C37:G37)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C37:G37)), "")</f>
-        <v/>
-      </c>
-      <c r="J37" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1" s="44">
-      <c r="A38" s="54" t="inlineStr">
-        <is>
-          <t>إجمالي عدد الساعات :</t>
-        </is>
-      </c>
-      <c r="B38" s="80" t="n"/>
-      <c r="C38" s="81">
-        <f>SUM(C7:C37) -  (COUNTIF(B7:B37, "AWO") * 8)</f>
-        <v/>
-      </c>
-      <c r="D38" s="82">
-        <f>IFERROR(SUM(D7:D37), "")</f>
-        <v/>
-      </c>
-      <c r="E38" s="82">
-        <f>IFERROR(SUM(E7:E37), "")</f>
-        <v/>
-      </c>
-      <c r="F38" s="82">
-        <f>IFERROR(SUM(F7:F37), "")</f>
-        <v/>
-      </c>
-      <c r="G38" s="13" t="n"/>
-      <c r="H38" s="83" t="n"/>
-      <c r="I38" s="32" t="inlineStr">
-        <is>
-          <t>الملاحظات :</t>
-        </is>
-      </c>
-      <c r="J38" s="84" t="n"/>
-    </row>
-    <row r="39" ht="30" customHeight="1" s="44">
-      <c r="A39" s="54" t="inlineStr">
-        <is>
-          <t>إجمالي عدد ايام الدوام :</t>
-        </is>
-      </c>
-      <c r="B39" s="80" t="n"/>
-      <c r="C39" s="85">
-        <f>COUNTIF(B7:B37, "P") + COUNTIF(B7:B37, "W") + COUNTIF(B7:B37, "H") + COUNTIF(B7:B37, "A") + COUNTIF(B7:B37, "AWO")-C40</f>
-        <v/>
-      </c>
-      <c r="D39" s="85" t="n"/>
-      <c r="E39" s="85" t="n"/>
-      <c r="F39" s="85" t="n"/>
-      <c r="G39" s="35" t="inlineStr">
-        <is>
-          <t>الاجازات المرضية</t>
-        </is>
-      </c>
-      <c r="H39" s="86">
-        <f>COUNTIF(B7:B37,"sl")</f>
-        <v/>
-      </c>
-      <c r="I39" s="46">
-        <f>COUNTIFS(G7:G37, "SL", G7:G37, "&lt;=3")</f>
-        <v/>
-      </c>
-      <c r="J39" s="84" t="n"/>
-    </row>
-    <row r="40" ht="37.2" customHeight="1" s="44">
-      <c r="A40" s="54" t="inlineStr">
-        <is>
-          <t>إجمالي عدد ايام الغياب :</t>
-        </is>
-      </c>
-      <c r="B40" s="80" t="n"/>
-      <c r="C40" s="85">
-        <f>COUNTIF(B7:B37,"A")+COUNTIF(B7:B37,"AWO")*2</f>
-        <v/>
-      </c>
-      <c r="D40" s="85" t="n"/>
-      <c r="E40" s="85" t="n"/>
-      <c r="F40" s="85" t="n"/>
-      <c r="G40" s="33" t="inlineStr">
-        <is>
-          <t>قيمة الخصم الاضافي</t>
-        </is>
-      </c>
-      <c r="H40" s="87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="47" t="n"/>
-      <c r="J40" s="84" t="n"/>
-    </row>
-    <row r="41" ht="37.2" customHeight="1" s="44">
-      <c r="A41" s="54" t="inlineStr">
-        <is>
-          <t>قيمة الخصم :</t>
-        </is>
-      </c>
-      <c r="B41" s="80" t="n"/>
-      <c r="C41" s="88">
-        <f>COUNTIF(B7:B37,"AWO") * 2 * I3 +COUNTIF(B7:B37, "A") * I3</f>
-        <v/>
-      </c>
-      <c r="D41" s="85" t="n"/>
-      <c r="E41" s="85" t="n"/>
-      <c r="F41" s="89" t="n"/>
-      <c r="G41" s="35" t="inlineStr">
-        <is>
-          <t>مجموع الخصم :</t>
-        </is>
-      </c>
-      <c r="H41" s="87">
-        <f>SUM(C41+H40)</f>
-        <v/>
-      </c>
-      <c r="I41" s="48" t="n"/>
-      <c r="J41" s="84" t="n"/>
-    </row>
-    <row r="42" ht="37.2" customHeight="1" s="44">
-      <c r="A42" s="54" t="inlineStr">
-        <is>
-          <t>إجمالي الأجر بعد الخصم :</t>
-        </is>
-      </c>
-      <c r="B42" s="80" t="n"/>
-      <c r="C42" s="90">
-        <f>IF(F4&lt;&gt;"", I2/(DAY(EOMONTH(F2,0))*8)*C38, "")</f>
-        <v/>
-      </c>
-      <c r="D42" s="90">
-        <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*1.25*D38, "")</f>
-        <v/>
-      </c>
-      <c r="E42" s="90">
-        <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*1.5*E38, "")</f>
-        <v/>
-      </c>
-      <c r="F42" s="90">
-        <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*2.5*F38, "")</f>
-        <v/>
-      </c>
-      <c r="G42" s="66" t="inlineStr">
-        <is>
-          <t>: الإجمالي</t>
-        </is>
-      </c>
-      <c r="H42" s="80" t="n"/>
-      <c r="I42" s="67">
-        <f>IFERROR(SUM(C42:F42), "") - H40</f>
-        <v/>
-      </c>
-      <c r="J42" s="84" t="n"/>
-    </row>
-    <row r="43" ht="34.2" customHeight="1" s="44">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">التاريخ : </t>
-        </is>
-      </c>
-      <c r="B43" s="91">
-        <f>TODAY()</f>
-        <v/>
-      </c>
-      <c r="C43" s="92" t="n"/>
-      <c r="D43" s="93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">توقيع الموظف : </t>
-        </is>
-      </c>
-      <c r="E43" s="93" t="n"/>
-      <c r="F43" s="93" t="n"/>
-      <c r="G43" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">توقيع المدير : </t>
-        </is>
-      </c>
-      <c r="H43" s="94" t="n"/>
-      <c r="I43" s="18" t="n"/>
-      <c r="J43" s="84" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="19" t="n"/>
-      <c r="B44" s="95" t="n"/>
-      <c r="C44" s="95" t="n"/>
-      <c r="D44" s="95" t="n"/>
-      <c r="E44" s="95" t="n"/>
-      <c r="F44" s="95" t="n"/>
-      <c r="G44" s="19" t="n"/>
-      <c r="H44" s="95" t="n"/>
-      <c r="I44" s="19" t="n"/>
-      <c r="J44" s="84" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="19" t="n"/>
-      <c r="B45" s="95" t="n"/>
-      <c r="C45" s="95" t="n"/>
-      <c r="D45" s="95" t="n"/>
-      <c r="E45" s="95" t="n"/>
-      <c r="F45" s="95" t="n"/>
-      <c r="G45" s="19" t="n"/>
-      <c r="H45" s="95" t="n"/>
-      <c r="I45" s="19" t="n"/>
-      <c r="J45" s="84" t="n"/>
-    </row>
-    <row r="46">
-      <c r="B46" s="84" t="n"/>
-      <c r="C46" s="84" t="n"/>
-      <c r="D46" s="84" t="n"/>
-      <c r="E46" s="84" t="n"/>
-      <c r="F46" s="84" t="n"/>
-      <c r="H46" s="84" t="n"/>
-      <c r="J46" s="84" t="n"/>
-    </row>
-    <row r="47">
-      <c r="B47" s="84" t="n"/>
-      <c r="C47" s="84" t="n"/>
-      <c r="D47" s="84" t="n"/>
-      <c r="E47" s="84" t="n"/>
-      <c r="F47" s="84" t="n"/>
-      <c r="H47" s="84" t="n"/>
-      <c r="J47" s="84" t="n"/>
-    </row>
-    <row r="48">
-      <c r="B48" s="84" t="n"/>
-      <c r="C48" s="84" t="n"/>
-      <c r="D48" s="84" t="n"/>
-      <c r="E48" s="84" t="n"/>
-      <c r="F48" s="84" t="n"/>
-      <c r="H48" s="84" t="n"/>
-      <c r="J48" s="84" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="84" t="n"/>
-      <c r="C49" s="84" t="n"/>
-      <c r="D49" s="84" t="n"/>
-      <c r="E49" s="84" t="n"/>
-      <c r="F49" s="84" t="n"/>
-      <c r="H49" s="84" t="n"/>
-      <c r="J49" s="84" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="45">
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="I39:I41"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="J37:P37"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="J34:P34"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="J36:P36"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="J35:P35"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="J7:P7"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="J25:P25"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="52" horizontalDpi="4294967293"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:P49"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="17.77734375" customWidth="1" style="44" min="1" max="1"/>
-    <col width="18.77734375" customWidth="1" style="44" min="2" max="2"/>
-    <col width="20.21875" customWidth="1" style="44" min="3" max="3"/>
-    <col width="18.21875" customWidth="1" style="44" min="4" max="4"/>
-    <col width="18.109375" customWidth="1" style="44" min="5" max="5"/>
-    <col width="18.21875" customWidth="1" style="44" min="6" max="6"/>
-    <col width="21.77734375" customWidth="1" style="44" min="7" max="7"/>
-    <col width="18.21875" customWidth="1" style="44" min="8" max="9"/>
-    <col width="8.77734375" customWidth="1" style="44" min="10" max="75"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="58.8" customHeight="1" s="44">
-      <c r="A1" s="59" t="n"/>
-      <c r="D1" s="45" t="inlineStr">
-        <is>
-          <t>بطاقة عامل</t>
-        </is>
-      </c>
-      <c r="F1" s="51" t="n"/>
-    </row>
-    <row r="2" ht="42.6" customHeight="1" s="44">
-      <c r="D2" s="57" t="n"/>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>بداية الشهر</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>46082</v>
-      </c>
-      <c r="G2" s="55" t="n"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>الراتب الاساسي :</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
           <t>1000</t>
         </is>
       </c>
@@ -17121,7 +15788,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>2500</t>
         </is>
       </c>
     </row>
@@ -17153,7 +15820,7 @@
       </c>
       <c r="B4" s="58" t="inlineStr">
         <is>
-          <t>محمد جمعة</t>
+          <t>وزير خان حبيب الله خان</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -17241,7 +15908,7 @@
       </c>
       <c r="B7" s="68" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C7" s="68" t="n">
@@ -17285,7 +15952,7 @@
       </c>
       <c r="H8" s="75" t="inlineStr">
         <is>
-          <t>Saqia 72</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I8" s="34">
@@ -17317,7 +15984,7 @@
       </c>
       <c r="H9" s="69" t="inlineStr">
         <is>
-          <t>Saqia 72</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I9" s="28">
@@ -17349,7 +16016,7 @@
       </c>
       <c r="H10" s="75" t="inlineStr">
         <is>
-          <t>Saqia 72</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I10" s="34">
@@ -17381,7 +16048,7 @@
       </c>
       <c r="H11" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I11" s="28">
@@ -17413,7 +16080,7 @@
       </c>
       <c r="H12" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I12" s="34">
@@ -17445,7 +16112,7 @@
       </c>
       <c r="H13" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I13" s="28">
@@ -17479,7 +16146,7 @@
       </c>
       <c r="H14" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I14" s="34">
@@ -17511,7 +16178,7 @@
       </c>
       <c r="H15" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I15" s="28">
@@ -17543,7 +16210,7 @@
       </c>
       <c r="H16" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I16" s="34">
@@ -17575,7 +16242,7 @@
       </c>
       <c r="H17" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I17" s="28">
@@ -17607,7 +16274,7 @@
       </c>
       <c r="H18" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I18" s="34">
@@ -17639,7 +16306,7 @@
       </c>
       <c r="H19" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I19" s="28">
@@ -17671,7 +16338,7 @@
       </c>
       <c r="H20" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I20" s="34">
@@ -17737,7 +16404,7 @@
       </c>
       <c r="H22" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I22" s="34">
@@ -17769,7 +16436,7 @@
       </c>
       <c r="H23" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I23" s="28">
@@ -17801,7 +16468,7 @@
       </c>
       <c r="H24" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I24" s="34">
@@ -17833,7 +16500,7 @@
       </c>
       <c r="H25" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I25" s="28">
@@ -17867,7 +16534,7 @@
       </c>
       <c r="H26" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I26" s="34">
@@ -17901,7 +16568,7 @@
       </c>
       <c r="H27" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I27" s="28">
@@ -17935,7 +16602,7 @@
       </c>
       <c r="H28" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I28" s="34">
@@ -17969,7 +16636,7 @@
       </c>
       <c r="H29" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I29" s="28">
@@ -18035,7 +16702,7 @@
       </c>
       <c r="H31" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I31" s="28">
@@ -18069,7 +16736,7 @@
       </c>
       <c r="H32" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I32" s="34">
@@ -18101,7 +16768,7 @@
       </c>
       <c r="H33" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I33" s="28">
@@ -18133,7 +16800,7 @@
       </c>
       <c r="H34" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I34" s="34">
@@ -18167,7 +16834,7 @@
       </c>
       <c r="H35" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I35" s="28">
@@ -18196,7 +16863,7 @@
       <c r="G36" s="29" t="n"/>
       <c r="H36" s="75" t="inlineStr">
         <is>
-          <t>Faya 334</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I36" s="34">
@@ -18225,7 +16892,7 @@
       <c r="G37" s="26" t="n"/>
       <c r="H37" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I37" s="28">
@@ -18571,7 +17238,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2600</t>
         </is>
       </c>
     </row>
@@ -18603,7 +17270,7 @@
       </c>
       <c r="B4" s="58" t="inlineStr">
         <is>
-          <t>وزير خان حبيب الله خان</t>
+          <t>عبدالودود عجب خان</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -18735,7 +17402,7 @@
       </c>
       <c r="H8" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saqia 72</t>
         </is>
       </c>
       <c r="I8" s="34">
@@ -18767,7 +17434,7 @@
       </c>
       <c r="H9" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saqia 72</t>
         </is>
       </c>
       <c r="I9" s="28">
@@ -18799,7 +17466,7 @@
       </c>
       <c r="H10" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Saqia 72</t>
         </is>
       </c>
       <c r="I10" s="34">
@@ -18831,7 +17498,7 @@
       </c>
       <c r="H11" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I11" s="28">
@@ -18863,7 +17530,7 @@
       </c>
       <c r="H12" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I12" s="34">
@@ -18895,7 +17562,7 @@
       </c>
       <c r="H13" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I13" s="28">
@@ -18929,7 +17596,7 @@
       </c>
       <c r="H14" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I14" s="34">
@@ -18961,7 +17628,7 @@
       </c>
       <c r="H15" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I15" s="28">
@@ -18993,7 +17660,7 @@
       </c>
       <c r="H16" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I16" s="34">
@@ -19025,7 +17692,7 @@
       </c>
       <c r="H17" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I17" s="28">
@@ -19057,7 +17724,7 @@
       </c>
       <c r="H18" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I18" s="34">
@@ -19089,7 +17756,7 @@
       </c>
       <c r="H19" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I19" s="28">
@@ -19121,7 +17788,7 @@
       </c>
       <c r="H20" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I20" s="34">
@@ -19155,7 +17822,7 @@
       </c>
       <c r="H21" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I21" s="28">
@@ -19187,7 +17854,7 @@
       </c>
       <c r="H22" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I22" s="34">
@@ -19219,7 +17886,7 @@
       </c>
       <c r="H23" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I23" s="28">
@@ -19251,7 +17918,7 @@
       </c>
       <c r="H24" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I24" s="34">
@@ -19283,7 +17950,7 @@
       </c>
       <c r="H25" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I25" s="28">
@@ -19317,7 +17984,7 @@
       </c>
       <c r="H26" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I26" s="34">
@@ -19385,7 +18052,7 @@
       </c>
       <c r="H28" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I28" s="34">
@@ -19419,7 +18086,7 @@
       </c>
       <c r="H29" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I29" s="28">
@@ -19453,7 +18120,7 @@
       </c>
       <c r="H30" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I30" s="34">
@@ -19519,7 +18186,7 @@
       </c>
       <c r="H32" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I32" s="34">
@@ -19551,7 +18218,7 @@
       </c>
       <c r="H33" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I33" s="28">
@@ -19617,7 +18284,7 @@
       </c>
       <c r="H35" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I35" s="28">
@@ -19646,7 +18313,7 @@
       <c r="G36" s="29" t="n"/>
       <c r="H36" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Faya 334</t>
         </is>
       </c>
       <c r="I36" s="34">
@@ -20021,7 +18688,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>1400</t>
         </is>
       </c>
     </row>
@@ -20053,7 +18720,7 @@
       </c>
       <c r="B4" s="58" t="inlineStr">
         <is>
-          <t>عبدالودود عجب خان</t>
+          <t>برينس كومار بانديت بهارات</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -20153,7 +18820,7 @@
       <c r="G7" s="26" t="n"/>
       <c r="H7" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I7" s="28">
@@ -20281,7 +18948,7 @@
       </c>
       <c r="H11" s="69" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I11" s="28">
@@ -20345,7 +19012,7 @@
       </c>
       <c r="H13" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I13" s="28">
@@ -20379,7 +19046,7 @@
       </c>
       <c r="H14" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I14" s="34">
@@ -20411,7 +19078,7 @@
       </c>
       <c r="H15" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I15" s="28">
@@ -20507,7 +19174,7 @@
       </c>
       <c r="H18" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I18" s="34">
@@ -20539,7 +19206,7 @@
       </c>
       <c r="H19" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I19" s="28">
@@ -20571,7 +19238,7 @@
       </c>
       <c r="H20" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I20" s="34">
@@ -20637,7 +19304,7 @@
       </c>
       <c r="H22" s="75" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I22" s="34">
@@ -20669,7 +19336,7 @@
       </c>
       <c r="H23" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I23" s="28">
@@ -20701,7 +19368,7 @@
       </c>
       <c r="H24" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I24" s="34">
@@ -20733,7 +19400,7 @@
       </c>
       <c r="H25" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I25" s="28">
@@ -20767,7 +19434,7 @@
       </c>
       <c r="H26" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I26" s="34">
@@ -20801,7 +19468,7 @@
       </c>
       <c r="H27" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I27" s="28">
@@ -20835,7 +19502,7 @@
       </c>
       <c r="H28" s="75" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I28" s="34">
@@ -20860,7 +19527,9 @@
       <c r="C29" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D29" s="68" t="n"/>
+      <c r="D29" s="68" t="n">
+        <v>2</v>
+      </c>
       <c r="E29" s="68" t="n"/>
       <c r="F29" s="68" t="n"/>
       <c r="G29" s="26">
@@ -20869,7 +19538,7 @@
       </c>
       <c r="H29" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I29" s="28">
@@ -20894,7 +19563,9 @@
       <c r="C30" s="72" t="n">
         <v>8</v>
       </c>
-      <c r="D30" s="71" t="n"/>
+      <c r="D30" s="71" t="n">
+        <v>2</v>
+      </c>
       <c r="E30" s="74" t="n"/>
       <c r="F30" s="74" t="n"/>
       <c r="G30" s="29">
@@ -20903,7 +19574,7 @@
       </c>
       <c r="H30" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I30" s="34">
@@ -20926,7 +19597,9 @@
       <c r="C31" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D31" s="68" t="n"/>
+      <c r="D31" s="68" t="n">
+        <v>2</v>
+      </c>
       <c r="E31" s="68" t="n"/>
       <c r="F31" s="68" t="n"/>
       <c r="G31" s="26">
@@ -20960,7 +19633,9 @@
       <c r="C32" s="72" t="n">
         <v>8</v>
       </c>
-      <c r="D32" s="71" t="n"/>
+      <c r="D32" s="71" t="n">
+        <v>2</v>
+      </c>
       <c r="E32" s="74" t="n"/>
       <c r="F32" s="74" t="n"/>
       <c r="G32" s="29">
@@ -20992,7 +19667,9 @@
       <c r="C33" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D33" s="68" t="n"/>
+      <c r="D33" s="68" t="n">
+        <v>1</v>
+      </c>
       <c r="E33" s="68" t="n"/>
       <c r="F33" s="68" t="n"/>
       <c r="G33" s="26">
@@ -21058,7 +19735,9 @@
       <c r="C35" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D35" s="68" t="n"/>
+      <c r="D35" s="68" t="n">
+        <v>2</v>
+      </c>
       <c r="E35" s="68" t="n"/>
       <c r="F35" s="68" t="n"/>
       <c r="G35" s="26">
@@ -21067,7 +19746,7 @@
       </c>
       <c r="H35" s="69" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I35" s="28">
@@ -21090,13 +19769,15 @@
       <c r="C36" s="72" t="n">
         <v>8</v>
       </c>
-      <c r="D36" s="74" t="n"/>
+      <c r="D36" s="74" t="n">
+        <v>2</v>
+      </c>
       <c r="E36" s="74" t="n"/>
       <c r="F36" s="74" t="n"/>
       <c r="G36" s="29" t="n"/>
       <c r="H36" s="75" t="inlineStr">
         <is>
-          <t>Faya 334</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I36" s="34">
@@ -21119,7 +19800,9 @@
       <c r="C37" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D37" s="68" t="n"/>
+      <c r="D37" s="68" t="n">
+        <v>2</v>
+      </c>
       <c r="E37" s="68" t="n"/>
       <c r="F37" s="68" t="n"/>
       <c r="G37" s="26" t="n"/>
@@ -21503,7 +20186,7 @@
       </c>
       <c r="B4" s="58" t="inlineStr">
         <is>
-          <t>برينس كومار بانديت بهارات</t>
+          <t>راما كانت ياداف سانترا ج ياداف</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -21635,7 +20318,7 @@
       </c>
       <c r="H8" s="75" t="inlineStr">
         <is>
-          <t>Saqia 72</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I8" s="34">
@@ -21667,7 +20350,7 @@
       </c>
       <c r="H9" s="69" t="inlineStr">
         <is>
-          <t>Saqia 72</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I9" s="28">
@@ -21699,7 +20382,7 @@
       </c>
       <c r="H10" s="75" t="inlineStr">
         <is>
-          <t>Saqia 72</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I10" s="34">
@@ -21763,7 +20446,7 @@
       </c>
       <c r="H12" s="75" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I12" s="34">
@@ -21795,7 +20478,7 @@
       </c>
       <c r="H13" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I13" s="28">
@@ -21957,7 +20640,7 @@
       </c>
       <c r="H18" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I18" s="34">
@@ -21989,7 +20672,7 @@
       </c>
       <c r="H19" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I19" s="28">
@@ -22021,7 +20704,7 @@
       </c>
       <c r="H20" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I20" s="34">
@@ -22321,7 +21004,7 @@
       </c>
       <c r="H29" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I29" s="28">
@@ -22357,7 +21040,7 @@
       </c>
       <c r="H30" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I30" s="34">
@@ -22937,7 +21620,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1100</t>
         </is>
       </c>
     </row>
@@ -22969,7 +21652,7 @@
       </c>
       <c r="B4" s="58" t="inlineStr">
         <is>
-          <t>راما كانت ياداف سانترا ج ياداف</t>
+          <t>نظر جان محمد ظاهر</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -23069,7 +21752,7 @@
       <c r="G7" s="26" t="n"/>
       <c r="H7" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I7" s="28">
@@ -23101,7 +21784,7 @@
       </c>
       <c r="H8" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I8" s="34">
@@ -23133,7 +21816,7 @@
       </c>
       <c r="H9" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I9" s="28">
@@ -23165,7 +21848,7 @@
       </c>
       <c r="H10" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I10" s="34">
@@ -23188,7 +21871,9 @@
       <c r="C11" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="68" t="n"/>
+      <c r="D11" s="68" t="n">
+        <v>3</v>
+      </c>
       <c r="E11" s="68" t="n"/>
       <c r="F11" s="68" t="n"/>
       <c r="G11" s="26">
@@ -23197,15 +21882,17 @@
       </c>
       <c r="H11" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I11" s="28">
         <f>IFERROR(IF(SUM(C11:G11)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C11:G11)), "")</f>
         <v/>
       </c>
-      <c r="J11" s="70" t="n">
-        <v/>
+      <c r="J11" s="70" t="inlineStr">
+        <is>
+          <t>تنزيل حديد</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" s="44">
@@ -23220,7 +21907,9 @@
       <c r="C12" s="72" t="n">
         <v>8</v>
       </c>
-      <c r="D12" s="71" t="n"/>
+      <c r="D12" s="71" t="n">
+        <v>3</v>
+      </c>
       <c r="E12" s="73" t="n"/>
       <c r="F12" s="74" t="n"/>
       <c r="G12" s="29">
@@ -23229,15 +21918,17 @@
       </c>
       <c r="H12" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I12" s="34">
         <f>IFERROR(IF(SUM(C12:G12)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C12:G12)), "")</f>
         <v/>
       </c>
-      <c r="J12" s="70" t="n">
-        <v/>
+      <c r="J12" s="70" t="inlineStr">
+        <is>
+          <t>تنزيل طابوق</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" s="44">
@@ -23261,7 +21952,7 @@
       </c>
       <c r="H13" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I13" s="28">
@@ -23286,7 +21977,9 @@
       <c r="C14" s="72" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="71" t="n"/>
+      <c r="D14" s="71" t="n">
+        <v>3</v>
+      </c>
       <c r="E14" s="74" t="n"/>
       <c r="F14" s="74" t="n"/>
       <c r="G14" s="29">
@@ -23295,15 +21988,17 @@
       </c>
       <c r="H14" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I14" s="34">
         <f>IFERROR(IF(SUM(C14:G14)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C14:G14)), "")</f>
         <v/>
       </c>
-      <c r="J14" s="70" t="n">
-        <v/>
+      <c r="J14" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تكسير الخرسانة </t>
+        </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" s="44">
@@ -23327,7 +22022,7 @@
       </c>
       <c r="H15" s="69" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I15" s="28">
@@ -23359,7 +22054,7 @@
       </c>
       <c r="H16" s="75" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I16" s="34">
@@ -23391,7 +22086,7 @@
       </c>
       <c r="H17" s="69" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I17" s="28">
@@ -23423,7 +22118,7 @@
       </c>
       <c r="H18" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I18" s="34">
@@ -23455,7 +22150,7 @@
       </c>
       <c r="H19" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I19" s="28">
@@ -23487,7 +22182,7 @@
       </c>
       <c r="H20" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I20" s="34">
@@ -23521,7 +22216,7 @@
       </c>
       <c r="H21" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I21" s="28">
@@ -23553,7 +22248,7 @@
       </c>
       <c r="H22" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I22" s="34">
@@ -23585,7 +22280,7 @@
       </c>
       <c r="H23" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I23" s="28">
@@ -23617,7 +22312,7 @@
       </c>
       <c r="H24" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I24" s="34">
@@ -23649,7 +22344,7 @@
       </c>
       <c r="H25" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I25" s="28">
@@ -23683,7 +22378,7 @@
       </c>
       <c r="H26" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I26" s="34">
@@ -23717,7 +22412,7 @@
       </c>
       <c r="H27" s="69" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I27" s="28">
@@ -23751,7 +22446,7 @@
       </c>
       <c r="H28" s="75" t="inlineStr">
         <is>
-          <t>Saeed Al Zubaidi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I28" s="34">
@@ -23787,7 +22482,7 @@
       </c>
       <c r="H29" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I29" s="28">
@@ -23823,7 +22518,7 @@
       </c>
       <c r="H30" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I30" s="34">
@@ -23857,7 +22552,7 @@
       </c>
       <c r="H31" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I31" s="28">
@@ -23893,7 +22588,7 @@
       </c>
       <c r="H32" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I32" s="34">
@@ -23927,7 +22622,7 @@
       </c>
       <c r="H33" s="69" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I33" s="28">
@@ -23959,7 +22654,7 @@
       </c>
       <c r="H34" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I34" s="34">
@@ -24026,7 +22721,7 @@
       <c r="G36" s="29" t="n"/>
       <c r="H36" s="75" t="inlineStr">
         <is>
-          <t>Salem Al Zaabi</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I36" s="34">
@@ -24403,7 +23098,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1200</t>
         </is>
       </c>
     </row>
@@ -24435,7 +23130,7 @@
       </c>
       <c r="B4" s="58" t="inlineStr">
         <is>
-          <t>نظر جان محمد ظاهر</t>
+          <t>ارشد على عزيز اور الرحمن</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -24535,7 +23230,7 @@
       <c r="G7" s="26" t="n"/>
       <c r="H7" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I7" s="28">
@@ -24567,7 +23262,7 @@
       </c>
       <c r="H8" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I8" s="34">
@@ -24599,7 +23294,7 @@
       </c>
       <c r="H9" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I9" s="28">
@@ -24690,9 +23385,7 @@
       <c r="C12" s="72" t="n">
         <v>8</v>
       </c>
-      <c r="D12" s="71" t="n">
-        <v>3</v>
-      </c>
+      <c r="D12" s="71" t="n"/>
       <c r="E12" s="73" t="n"/>
       <c r="F12" s="74" t="n"/>
       <c r="G12" s="29">
@@ -24701,17 +23394,15 @@
       </c>
       <c r="H12" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I12" s="34">
         <f>IFERROR(IF(SUM(C12:G12)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C12:G12)), "")</f>
         <v/>
       </c>
-      <c r="J12" s="70" t="inlineStr">
-        <is>
-          <t>تنزيل طابوق</t>
-        </is>
+      <c r="J12" s="70" t="n">
+        <v/>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" s="44">
@@ -24727,7 +23418,9 @@
         <v>8</v>
       </c>
       <c r="D13" s="68" t="n"/>
-      <c r="E13" s="68" t="n"/>
+      <c r="E13" s="68" t="n">
+        <v>3</v>
+      </c>
       <c r="F13" s="68" t="n"/>
       <c r="G13" s="26">
         <f>IF(B13="SL","SL","")</f>
@@ -24744,7 +23437,7 @@
       </c>
       <c r="J13" s="70" t="inlineStr">
         <is>
-          <t>Weekend</t>
+          <t>Weekend تنزيل طابوق</t>
         </is>
       </c>
     </row>
@@ -24760,9 +23453,7 @@
       <c r="C14" s="72" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="71" t="n">
-        <v>3</v>
-      </c>
+      <c r="D14" s="71" t="n"/>
       <c r="E14" s="74" t="n"/>
       <c r="F14" s="74" t="n"/>
       <c r="G14" s="29">
@@ -24771,17 +23462,15 @@
       </c>
       <c r="H14" s="75" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Abdullah Aljunaibi</t>
         </is>
       </c>
       <c r="I14" s="34">
         <f>IFERROR(IF(SUM(C14:G14)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C14:G14)), "")</f>
         <v/>
       </c>
-      <c r="J14" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تكسير الخرسانة </t>
-        </is>
+      <c r="J14" s="70" t="n">
+        <v/>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" s="44">
@@ -24837,7 +23526,7 @@
       </c>
       <c r="H16" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I16" s="34">
@@ -24869,7 +23558,7 @@
       </c>
       <c r="H17" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I17" s="28">
@@ -24965,7 +23654,7 @@
       </c>
       <c r="H20" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I20" s="34">
@@ -24999,15 +23688,17 @@
       </c>
       <c r="H21" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I21" s="28">
         <f>IFERROR(IF(SUM(C21:G21)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C21:G21)), "")</f>
         <v/>
       </c>
-      <c r="J21" s="70" t="n">
-        <v/>
+      <c r="J21" s="70" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1" s="44">
@@ -25031,7 +23722,7 @@
       </c>
       <c r="H22" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I22" s="34">
@@ -25054,7 +23745,9 @@
       <c r="C23" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D23" s="68" t="n"/>
+      <c r="D23" s="68" t="n">
+        <v>3</v>
+      </c>
       <c r="E23" s="68" t="n"/>
       <c r="F23" s="68" t="n"/>
       <c r="G23" s="26">
@@ -25063,15 +23756,17 @@
       </c>
       <c r="H23" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I23" s="28">
         <f>IFERROR(IF(SUM(C23:G23)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C23:G23)), "")</f>
         <v/>
       </c>
-      <c r="J23" s="70" t="n">
-        <v/>
+      <c r="J23" s="70" t="inlineStr">
+        <is>
+          <t>عمل إضافي في المزرعة</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1" s="44">
@@ -25095,7 +23790,7 @@
       </c>
       <c r="H24" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I24" s="34">
@@ -25127,7 +23822,7 @@
       </c>
       <c r="H25" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I25" s="28">
@@ -25161,7 +23856,7 @@
       </c>
       <c r="H26" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I26" s="34">
@@ -25229,7 +23924,7 @@
       </c>
       <c r="H28" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I28" s="34">
@@ -25301,7 +23996,7 @@
       </c>
       <c r="H30" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Farm 826</t>
         </is>
       </c>
       <c r="I30" s="34">
@@ -25335,7 +24030,7 @@
       </c>
       <c r="H31" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I31" s="28">
@@ -25371,7 +24066,7 @@
       </c>
       <c r="H32" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I32" s="34">
@@ -25405,7 +24100,7 @@
       </c>
       <c r="H33" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I33" s="28">
@@ -25437,7 +24132,7 @@
       </c>
       <c r="H34" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I34" s="34">
@@ -25473,7 +24168,7 @@
       </c>
       <c r="H35" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Waleed Al Amari</t>
         </is>
       </c>
       <c r="I35" s="28">
@@ -25881,7 +24576,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>3000</t>
         </is>
       </c>
     </row>
@@ -25913,7 +24608,7 @@
       </c>
       <c r="B4" s="58" t="inlineStr">
         <is>
-          <t>ارشد على عزيز اور الرحمن</t>
+          <t>محمد مصطفى يوسف  غانم</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -26013,7 +24708,7 @@
       <c r="G7" s="26" t="n"/>
       <c r="H7" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I7" s="28">
@@ -26045,7 +24740,7 @@
       </c>
       <c r="H8" s="75" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I8" s="34">
@@ -26077,7 +24772,7 @@
       </c>
       <c r="H9" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I9" s="28">
@@ -26109,7 +24804,7 @@
       </c>
       <c r="H10" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I10" s="34">
@@ -26132,9 +24827,7 @@
       <c r="C11" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="68" t="n">
-        <v>3</v>
-      </c>
+      <c r="D11" s="68" t="n"/>
       <c r="E11" s="68" t="n"/>
       <c r="F11" s="68" t="n"/>
       <c r="G11" s="26">
@@ -26143,17 +24836,15 @@
       </c>
       <c r="H11" s="69" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I11" s="28">
         <f>IFERROR(IF(SUM(C11:G11)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C11:G11)), "")</f>
         <v/>
       </c>
-      <c r="J11" s="70" t="inlineStr">
-        <is>
-          <t>تنزيل حديد</t>
-        </is>
+      <c r="J11" s="70" t="n">
+        <v/>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" s="44">
@@ -26177,7 +24868,7 @@
       </c>
       <c r="H12" s="75" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Saeed Al Zubaidi</t>
         </is>
       </c>
       <c r="I12" s="34">
@@ -26200,9 +24891,7 @@
       <c r="C13" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D13" s="68" t="n">
-        <v>3</v>
-      </c>
+      <c r="D13" s="68" t="n"/>
       <c r="E13" s="68" t="n"/>
       <c r="F13" s="68" t="n"/>
       <c r="G13" s="26">
@@ -26211,7 +24900,7 @@
       </c>
       <c r="H13" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I13" s="28">
@@ -26220,7 +24909,7 @@
       </c>
       <c r="J13" s="70" t="inlineStr">
         <is>
-          <t>Weekend تنزيل طابوق</t>
+          <t>Weekend</t>
         </is>
       </c>
     </row>
@@ -26245,7 +24934,7 @@
       </c>
       <c r="H14" s="75" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I14" s="34">
@@ -26277,7 +24966,7 @@
       </c>
       <c r="H15" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I15" s="28">
@@ -26309,7 +24998,7 @@
       </c>
       <c r="H16" s="75" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I16" s="34">
@@ -26341,7 +25030,7 @@
       </c>
       <c r="H17" s="69" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I17" s="28">
@@ -26471,17 +25160,15 @@
       </c>
       <c r="H21" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I21" s="28">
         <f>IFERROR(IF(SUM(C21:G21)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C21:G21)), "")</f>
         <v/>
       </c>
-      <c r="J21" s="70" t="inlineStr">
-        <is>
-          <t>Weekend</t>
-        </is>
+      <c r="J21" s="70" t="n">
+        <v/>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1" s="44">
@@ -26505,7 +25192,7 @@
       </c>
       <c r="H22" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I22" s="34">
@@ -26528,9 +25215,7 @@
       <c r="C23" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="D23" s="68" t="n">
-        <v>3</v>
-      </c>
+      <c r="D23" s="68" t="n"/>
       <c r="E23" s="68" t="n"/>
       <c r="F23" s="68" t="n"/>
       <c r="G23" s="26">
@@ -26539,17 +25224,15 @@
       </c>
       <c r="H23" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I23" s="28">
         <f>IFERROR(IF(SUM(C23:G23)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C23:G23)), "")</f>
         <v/>
       </c>
-      <c r="J23" s="70" t="inlineStr">
-        <is>
-          <t>عمل إضافي في المزرعة</t>
-        </is>
+      <c r="J23" s="70" t="n">
+        <v/>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1" s="44">
@@ -26573,7 +25256,7 @@
       </c>
       <c r="H24" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I24" s="34">
@@ -26605,7 +25288,7 @@
       </c>
       <c r="H25" s="69" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I25" s="28">
@@ -26639,7 +25322,7 @@
       </c>
       <c r="H26" s="75" t="inlineStr">
         <is>
-          <t>Farm 826</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I26" s="34">
@@ -26673,7 +25356,7 @@
       </c>
       <c r="H27" s="69" t="inlineStr">
         <is>
-          <t>Abdullah Aljunaibi</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I27" s="28">
@@ -26707,7 +25390,7 @@
       </c>
       <c r="H28" s="75" t="inlineStr">
         <is>
-          <t>Waleed Al Amari</t>
+          <t>Salem Al Zaabi</t>
         </is>
       </c>
       <c r="I28" s="34">
@@ -26726,25 +25409,19 @@
       </c>
       <c r="B29" s="68" t="inlineStr">
         <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C29" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D29" s="68" t="n">
-        <v>2</v>
-      </c>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C29" s="68" t="n"/>
+      <c r="D29" s="68" t="n"/>
       <c r="E29" s="68" t="n"/>
       <c r="F29" s="68" t="n"/>
       <c r="G29" s="26">
         <f>IF(B29="SL","SL","")</f>
         <v/>
       </c>
-      <c r="H29" s="69" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
+      <c r="H29" s="69" t="n">
+        <v/>
       </c>
       <c r="I29" s="28">
         <f>IFERROR(IF(SUM(C29:G29)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C29:G29)), "")</f>
@@ -26752,7 +25429,7 @@
       </c>
       <c r="J29" s="70" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>Last day was 22 Mar</t>
         </is>
       </c>
     </row>
@@ -26762,25 +25439,19 @@
       </c>
       <c r="B30" s="71" t="inlineStr">
         <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C30" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D30" s="71" t="n">
-        <v>2</v>
-      </c>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C30" s="72" t="n"/>
+      <c r="D30" s="71" t="n"/>
       <c r="E30" s="74" t="n"/>
       <c r="F30" s="74" t="n"/>
       <c r="G30" s="29">
         <f>IF(B30="SL","SL","")</f>
         <v/>
       </c>
-      <c r="H30" s="75" t="inlineStr">
-        <is>
-          <t>Farm 826</t>
-        </is>
+      <c r="H30" s="75" t="n">
+        <v/>
       </c>
       <c r="I30" s="34">
         <f>IFERROR(IF(SUM(C30:G30)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C30:G30)), "")</f>
@@ -26790,122 +25461,64 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="32" customHeight="1" s="44">
-      <c r="A31" s="61" t="n">
-        <v>46106</v>
-      </c>
-      <c r="B31" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C31" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D31" s="68" t="n">
-        <v>2</v>
-      </c>
+    <row r="31" ht="30" customHeight="1" s="44">
+      <c r="A31" s="61" t="n"/>
+      <c r="B31" s="68" t="n"/>
+      <c r="C31" s="68" t="n"/>
+      <c r="D31" s="68" t="n"/>
       <c r="E31" s="68" t="n"/>
       <c r="F31" s="68" t="n"/>
       <c r="G31" s="26">
         <f>IF(B31="SL","SL","")</f>
         <v/>
       </c>
-      <c r="H31" s="69" t="inlineStr">
-        <is>
-          <t>Salem Al Zaabi</t>
-        </is>
-      </c>
+      <c r="H31" s="69" t="n"/>
       <c r="I31" s="28">
         <f>IFERROR(IF(SUM(C31:G31)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C31:G31)), "")</f>
         <v/>
       </c>
-      <c r="J31" s="70" t="inlineStr">
-        <is>
-          <t>Weekend</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1" s="44">
-      <c r="A32" s="62" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B32" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C32" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D32" s="71" t="n">
-        <v>2</v>
-      </c>
+      <c r="J31" s="96" t="n"/>
+    </row>
+    <row r="32" ht="30" customHeight="1" s="44">
+      <c r="A32" s="62" t="n"/>
+      <c r="B32" s="71" t="n"/>
+      <c r="C32" s="72" t="n"/>
+      <c r="D32" s="71" t="n"/>
       <c r="E32" s="74" t="n"/>
       <c r="F32" s="74" t="n"/>
       <c r="G32" s="29">
         <f>IF(B32="SL","SL","")</f>
         <v/>
       </c>
-      <c r="H32" s="75" t="inlineStr">
-        <is>
-          <t>Salem Al Zaabi</t>
-        </is>
-      </c>
+      <c r="H32" s="75" t="n"/>
       <c r="I32" s="34">
         <f>IFERROR(IF(SUM(C32:G32)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C32:G32)), "")</f>
         <v/>
       </c>
-      <c r="J32" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="32" customHeight="1" s="44">
-      <c r="A33" s="61" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B33" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C33" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D33" s="68" t="n">
-        <v>1</v>
-      </c>
+      <c r="J32" s="96" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1" s="44">
+      <c r="A33" s="61" t="n"/>
+      <c r="B33" s="68" t="n"/>
+      <c r="C33" s="68" t="n"/>
+      <c r="D33" s="68" t="n"/>
       <c r="E33" s="68" t="n"/>
       <c r="F33" s="68" t="n"/>
       <c r="G33" s="26">
         <f>IF(B33="SL","SL","")</f>
         <v/>
       </c>
-      <c r="H33" s="69" t="inlineStr">
-        <is>
-          <t>Waleed Al Amari</t>
-        </is>
-      </c>
+      <c r="H33" s="69" t="n"/>
       <c r="I33" s="28">
         <f>IFERROR(IF(SUM(C33:G33)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C33:G33)), "")</f>
         <v/>
       </c>
-      <c r="J33" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="32" customHeight="1" s="44">
-      <c r="A34" s="62" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B34" s="78" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="C34" s="72" t="n">
-        <v>8</v>
-      </c>
+      <c r="J33" s="96" t="n"/>
+    </row>
+    <row r="34" ht="30" customHeight="1" s="44">
+      <c r="A34" s="62" t="n"/>
+      <c r="B34" s="79" t="n"/>
+      <c r="C34" s="72" t="n"/>
       <c r="D34" s="74" t="n"/>
       <c r="E34" s="74" t="n"/>
       <c r="F34" s="74" t="n"/>
@@ -26913,116 +25526,60 @@
         <f>IF(B34="SL","SL","")</f>
         <v/>
       </c>
-      <c r="H34" s="75" t="inlineStr">
-        <is>
-          <t>Salem Al Zaabi</t>
-        </is>
-      </c>
+      <c r="H34" s="75" t="n"/>
       <c r="I34" s="34">
         <f>IFERROR(IF(SUM(C34:G34)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C34:G34)), "")</f>
         <v/>
       </c>
-      <c r="J34" s="70" t="inlineStr">
-        <is>
-          <t>Weekend</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="32" customHeight="1" s="44">
-      <c r="A35" s="61" t="n">
-        <v>46110</v>
-      </c>
-      <c r="B35" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C35" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D35" s="68" t="n">
-        <v>2</v>
-      </c>
+      <c r="J34" s="96" t="n"/>
+    </row>
+    <row r="35" ht="30" customHeight="1" s="44">
+      <c r="A35" s="61" t="n"/>
+      <c r="B35" s="68" t="n"/>
+      <c r="C35" s="68" t="n"/>
+      <c r="D35" s="68" t="n"/>
       <c r="E35" s="68" t="n"/>
       <c r="F35" s="68" t="n"/>
       <c r="G35" s="26">
         <f>IF(B35="SL","SL","")</f>
         <v/>
       </c>
-      <c r="H35" s="69" t="inlineStr">
-        <is>
-          <t>Waleed Al Amari</t>
-        </is>
-      </c>
+      <c r="H35" s="69" t="n"/>
       <c r="I35" s="28">
         <f>IFERROR(IF(SUM(C35:G35)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C35:G35)), "")</f>
         <v/>
       </c>
-      <c r="J35" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="32" customHeight="1" s="44">
-      <c r="A36" s="62" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B36" s="79" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C36" s="72" t="n">
-        <v>8</v>
-      </c>
-      <c r="D36" s="74" t="n">
-        <v>2</v>
-      </c>
+      <c r="J35" s="96" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1" s="44">
+      <c r="A36" s="62" t="n"/>
+      <c r="B36" s="79" t="n"/>
+      <c r="C36" s="72" t="n"/>
+      <c r="D36" s="74" t="n"/>
       <c r="E36" s="74" t="n"/>
       <c r="F36" s="74" t="n"/>
       <c r="G36" s="29" t="n"/>
-      <c r="H36" s="75" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
-      </c>
+      <c r="H36" s="75" t="n"/>
       <c r="I36" s="34">
         <f>IFERROR(IF(SUM(C36:G36)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C36:G36)), "")</f>
         <v/>
       </c>
-      <c r="J36" s="70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1" s="44">
-      <c r="A37" s="61" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B37" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C37" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="D37" s="68" t="n">
-        <v>2</v>
-      </c>
+      <c r="J36" s="96" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1" s="44">
+      <c r="A37" s="61" t="n"/>
+      <c r="B37" s="68" t="n"/>
+      <c r="C37" s="68" t="n"/>
+      <c r="D37" s="68" t="n"/>
       <c r="E37" s="68" t="n"/>
       <c r="F37" s="68" t="n"/>
       <c r="G37" s="26" t="n"/>
-      <c r="H37" s="69" t="inlineStr">
-        <is>
-          <t>Abdullah Aljunaibi</t>
-        </is>
-      </c>
+      <c r="H37" s="69" t="n"/>
       <c r="I37" s="28">
         <f>IFERROR(IF(SUM(C37:G37)&gt;24,"إجمالي &gt; 24 ساعة.",SUM(C37:G37)), "")</f>
         <v/>
       </c>
-      <c r="J37" s="70" t="n">
-        <v/>
-      </c>
+      <c r="J37" s="96" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1" s="44">
       <c r="A38" s="54" t="inlineStr">
